--- a/KAE Ausz KonPe KTZH.xlsx
+++ b/KAE Ausz KonPe KTZH.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Werkstatt\Amtsleitung\Monitoring Covid19\Archiv Versände\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\STAT\01_Post\Schlaepfer\covid19monitoring\economy_AWA_private\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -13,7 +13,6 @@
   </bookViews>
   <sheets>
     <sheet name="März 2020" sheetId="1" r:id="rId1"/>
-    <sheet name="April 2020" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
   <si>
     <t>Metriken</t>
   </si>
@@ -118,9 +117,6 @@
   </si>
   <si>
     <t>Total</t>
-  </si>
-  <si>
-    <t>April 2020</t>
   </si>
   <si>
     <t>C 29: Fahrzeugbau</t>
@@ -147,7 +143,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -201,7 +197,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -506,13 +502,13 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -605,13 +601,13 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -627,24 +623,24 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -770,13 +766,13 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -825,7 +821,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33">
         <v>40</v>
@@ -843,395 +839,6 @@
       </c>
       <c r="C34">
         <v>163524</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="58.5703125" customWidth="1"/>
-    <col min="2" max="2" width="39.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="3">
-        <v>75</v>
-      </c>
-      <c r="C3" s="3">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3">
-        <v>257</v>
-      </c>
-      <c r="C5" s="3">
-        <v>5219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="3">
-        <v>123</v>
-      </c>
-      <c r="C6" s="3">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="3">
-        <v>254</v>
-      </c>
-      <c r="C7" s="3">
-        <v>1632</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="3">
-        <v>43</v>
-      </c>
-      <c r="C8" s="3">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="3">
-        <v>51</v>
-      </c>
-      <c r="C9" s="3">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="3">
-        <v>173</v>
-      </c>
-      <c r="C10" s="3">
-        <v>1970</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="3">
-        <v>180</v>
-      </c>
-      <c r="C11" s="3">
-        <v>3263</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="3">
-        <v>124</v>
-      </c>
-      <c r="C12" s="3">
-        <v>2109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="3">
-        <v>14</v>
-      </c>
-      <c r="C13" s="3">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="3">
-        <v>272</v>
-      </c>
-      <c r="C14" s="3">
-        <v>2810</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="3">
-        <v>29</v>
-      </c>
-      <c r="C16" s="3">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="3">
-        <v>1186</v>
-      </c>
-      <c r="C17" s="3">
-        <v>6057</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="3">
-        <v>838</v>
-      </c>
-      <c r="C18" s="3">
-        <v>5307</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="3">
-        <v>1692</v>
-      </c>
-      <c r="C19" s="3">
-        <v>15059</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="3">
-        <v>1889</v>
-      </c>
-      <c r="C20" s="3">
-        <v>12163</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="3">
-        <v>621</v>
-      </c>
-      <c r="C21" s="3">
-        <v>18095</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="3">
-        <v>2841</v>
-      </c>
-      <c r="C22" s="3">
-        <v>30571</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="3">
-        <v>507</v>
-      </c>
-      <c r="C23" s="3">
-        <v>3440</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="3">
-        <v>369</v>
-      </c>
-      <c r="C24" s="3">
-        <v>1591</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="3">
-        <v>254</v>
-      </c>
-      <c r="C25" s="3">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="3">
-        <v>3196</v>
-      </c>
-      <c r="C26" s="3">
-        <v>26744</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="3">
-        <v>1432</v>
-      </c>
-      <c r="C27" s="3">
-        <v>28421</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="3">
-        <v>716</v>
-      </c>
-      <c r="C29" s="3">
-        <v>5962</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" s="3">
-        <v>2343</v>
-      </c>
-      <c r="C30" s="3">
-        <v>16793</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="3">
-        <v>778</v>
-      </c>
-      <c r="C31" s="3">
-        <v>8758</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32" s="3">
-        <v>1514</v>
-      </c>
-      <c r="C32" s="3">
-        <v>7223</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33">
-        <v>21</v>
-      </c>
-      <c r="C33">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34">
-        <v>21792</v>
-      </c>
-      <c r="C34">
-        <v>207916</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Ausz KonPe KTZH.xlsx
+++ b/KAE Ausz KonPe KTZH.xlsx
@@ -9,10 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="März 2020" sheetId="1" r:id="rId1"/>
+    <sheet name="April 2020" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="41">
   <si>
     <t>Metriken</t>
   </si>
@@ -119,6 +120,9 @@
     <t>Total</t>
   </si>
   <si>
+    <t>April 2020</t>
+  </si>
+  <si>
     <t>C 29: Fahrzeugbau</t>
   </si>
   <si>
@@ -131,13 +135,19 @@
     <t>D 35: Energieversorgung</t>
   </si>
   <si>
-    <t>O 84: Öffentliche Verwaltung, Verteidigung, Sozialversicherung</t>
-  </si>
-  <si>
     <t>Rest: Wirtschaftszweige mit &lt;10 Betriebsabteilungen oder &lt;100 abgerechneten Arbeitnehmern (mit NA gekennzeichnet)</t>
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>NOGA, konfektioniert</t>
+  </si>
+  <si>
+    <t>U: Übrige</t>
+  </si>
+  <si>
+    <t>Rest: Wirtschaftszweige mit &lt;10 Betriebsabteilungen oder &lt;100 abgerechneten Arbeitnehmern</t>
   </si>
 </sst>
 </file>
@@ -172,13 +182,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -459,22 +472,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="58.5703125" customWidth="1"/>
-    <col min="2" max="2" width="39.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
@@ -482,363 +495,767 @@
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2">
+        <v>80</v>
+      </c>
+      <c r="C5" s="2">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>220</v>
+      </c>
+      <c r="C7" s="2">
+        <v>4523</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>113</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>170</v>
+      </c>
+      <c r="C9" s="2">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>29</v>
+      </c>
+      <c r="C10" s="2">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>27</v>
+      </c>
+      <c r="C11" s="2">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>88</v>
+      </c>
+      <c r="C12" s="2">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>73</v>
+      </c>
+      <c r="C13" s="2">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>57</v>
+      </c>
+      <c r="C14" s="2">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>232</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2">
+        <v>865</v>
+      </c>
+      <c r="C19" s="2">
+        <v>3515</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2">
+        <v>734</v>
+      </c>
+      <c r="C20" s="2">
+        <v>3465</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2">
+        <v>1289</v>
+      </c>
+      <c r="C21" s="2">
+        <v>9861</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1860</v>
+      </c>
+      <c r="C22" s="2">
+        <v>12169</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2">
+        <v>520</v>
+      </c>
+      <c r="C23" s="2">
+        <v>16025</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2">
+        <v>3020</v>
+      </c>
+      <c r="C24" s="2">
+        <v>34035</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2">
+        <v>397</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2">
+        <v>294</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2">
+        <v>211</v>
+      </c>
+      <c r="C27" s="2">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2">
+        <v>2412</v>
+      </c>
+      <c r="C28" s="2">
+        <v>20693</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2">
+        <v>1199</v>
+      </c>
+      <c r="C29" s="2">
+        <v>23212</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="2">
+        <v>694</v>
+      </c>
+      <c r="C30" s="2">
+        <v>6131</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2">
+        <v>2096</v>
+      </c>
+      <c r="C31" s="2">
+        <v>11949</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="2">
+        <v>712</v>
+      </c>
+      <c r="C32" s="2">
+        <v>9176</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2">
+        <v>1556</v>
+      </c>
+      <c r="C33" s="2">
+        <v>6606</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="2">
+        <v>18989</v>
+      </c>
+      <c r="C36" s="2">
+        <v>173955</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="58.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>31</v>
+      </c>
       <c r="C2" s="2" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="1"/>
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3">
-        <v>75</v>
-      </c>
-      <c r="C3" s="3">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="B5" s="2">
+        <v>85</v>
+      </c>
+      <c r="C5" s="2">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>264</v>
+      </c>
+      <c r="C7" s="2">
+        <v>5424</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>131</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>277</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>52</v>
+      </c>
+      <c r="C10" s="2">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>63</v>
+      </c>
+      <c r="C11" s="2">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>197</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>194</v>
+      </c>
+      <c r="C13" s="2">
+        <v>4693</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>142</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>286</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2930</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3">
-        <v>209</v>
-      </c>
-      <c r="C5" s="3">
-        <v>4385</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="3">
-        <v>110</v>
-      </c>
-      <c r="C6" s="3">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="3">
-        <v>169</v>
-      </c>
-      <c r="C7" s="3">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="3">
+      <c r="B18" s="2">
+        <v>30</v>
+      </c>
+      <c r="C18" s="2">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2">
+        <v>1282</v>
+      </c>
+      <c r="C19" s="2">
+        <v>6461</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2">
+        <v>914</v>
+      </c>
+      <c r="C20" s="2">
+        <v>5619</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2">
+        <v>1835</v>
+      </c>
+      <c r="C21" s="2">
+        <v>18075</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1998</v>
+      </c>
+      <c r="C22" s="2">
+        <v>13472</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2">
+        <v>676</v>
+      </c>
+      <c r="C23" s="2">
+        <v>19766</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2">
+        <v>2966</v>
+      </c>
+      <c r="C24" s="2">
+        <v>31222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2">
+        <v>546</v>
+      </c>
+      <c r="C25" s="2">
+        <v>5194</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2">
+        <v>399</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2">
+        <v>277</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2">
+        <v>3500</v>
+      </c>
+      <c r="C28" s="2">
+        <v>31620</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2">
+        <v>1609</v>
+      </c>
+      <c r="C29" s="2">
+        <v>30304</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="2">
+        <v>785</v>
+      </c>
+      <c r="C30" s="2">
+        <v>7662</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="3">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="3">
-        <v>26</v>
-      </c>
-      <c r="C9" s="3">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="3">
-        <v>88</v>
-      </c>
-      <c r="C10" s="3">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="3">
-        <v>72</v>
-      </c>
-      <c r="C11" s="3">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="3">
-        <v>54</v>
-      </c>
-      <c r="C12" s="3">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="3">
-        <v>229</v>
-      </c>
-      <c r="C14" s="3">
-        <v>1805</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="3">
-        <v>836</v>
-      </c>
-      <c r="C17" s="3">
-        <v>3459</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="3">
-        <v>702</v>
-      </c>
-      <c r="C18" s="3">
-        <v>3347</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="3">
-        <v>1254</v>
-      </c>
-      <c r="C19" s="3">
-        <v>8518</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="3">
-        <v>1813</v>
-      </c>
-      <c r="C20" s="3">
-        <v>11346</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="3">
-        <v>501</v>
-      </c>
-      <c r="C21" s="3">
-        <v>15595</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="3">
-        <v>2972</v>
-      </c>
-      <c r="C22" s="3">
-        <v>33726</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="3">
-        <v>383</v>
-      </c>
-      <c r="C23" s="3">
-        <v>2110</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="B31" s="2">
+        <v>2600</v>
+      </c>
+      <c r="C31" s="2">
+        <v>19101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="2">
+        <v>828</v>
+      </c>
+      <c r="C32" s="2">
+        <v>10952</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2">
+        <v>1610</v>
+      </c>
+      <c r="C33" s="2">
+        <v>8127</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="2">
         <v>22</v>
       </c>
-      <c r="B24" s="3">
-        <v>284</v>
-      </c>
-      <c r="C24" s="3">
-        <v>1205</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="3">
-        <v>204</v>
-      </c>
-      <c r="C25" s="3">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="3">
-        <v>2306</v>
-      </c>
-      <c r="C26" s="3">
-        <v>18335</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="3">
-        <v>1140</v>
-      </c>
-      <c r="C27" s="3">
-        <v>22980</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="3">
-        <v>674</v>
-      </c>
-      <c r="C29" s="3">
-        <v>5893</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" s="3">
-        <v>2017</v>
-      </c>
-      <c r="C30" s="3">
-        <v>11481</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="3">
-        <v>685</v>
-      </c>
-      <c r="C31" s="3">
-        <v>7334</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32" s="3">
-        <v>1518</v>
-      </c>
-      <c r="C32" s="3">
-        <v>6490</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33">
-        <v>40</v>
-      </c>
-      <c r="C33">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
+      <c r="C35" s="2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B34">
-        <v>18388</v>
-      </c>
-      <c r="C34">
-        <v>163524</v>
+      <c r="B36" s="2">
+        <v>23582</v>
+      </c>
+      <c r="C36" s="2">
+        <v>235509</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Ausz KonPe KTZH.xlsx
+++ b/KAE Ausz KonPe KTZH.xlsx
@@ -9,11 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="März 2020" sheetId="1" r:id="rId1"/>
     <sheet name="April 2020" sheetId="2" r:id="rId2"/>
+    <sheet name="Mai 2020" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="42">
   <si>
     <t>Metriken</t>
   </si>
@@ -148,6 +149,9 @@
   </si>
   <si>
     <t>Rest: Wirtschaftszweige mit &lt;10 Betriebsabteilungen oder &lt;100 abgerechneten Arbeitnehmern</t>
+  </si>
+  <si>
+    <t>Mai 2020</t>
   </si>
 </sst>
 </file>
@@ -182,13 +186,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
@@ -508,18 +515,18 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C5" s="2">
-        <v>636</v>
+        <v>642</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -530,18 +537,18 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C7" s="2">
-        <v>4523</v>
+        <v>4431</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="2">
@@ -552,18 +559,18 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C9" s="2">
         <v>902</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="2">
@@ -574,18 +581,18 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="2">
         <v>326</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="2">
@@ -596,29 +603,29 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C13" s="2">
         <v>485</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C14" s="2">
-        <v>749</v>
+        <v>775</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -629,18 +636,18 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C16" s="2">
-        <v>1816</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -651,7 +658,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -662,179 +669,179 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>865</v>
+        <v>887</v>
       </c>
       <c r="C19" s="2">
-        <v>3515</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>734</v>
+        <v>748</v>
       </c>
       <c r="C20" s="2">
-        <v>3465</v>
+        <v>3506</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1289</v>
+        <v>1308</v>
       </c>
       <c r="C21" s="2">
-        <v>9861</v>
+        <v>9859</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1860</v>
+        <v>1884</v>
       </c>
       <c r="C22" s="2">
-        <v>12169</v>
+        <v>12064</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="C23" s="2">
-        <v>16025</v>
+        <v>16042</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3020</v>
+        <v>3049</v>
       </c>
       <c r="C24" s="2">
-        <v>34035</v>
+        <v>34093</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="C25" s="2">
-        <v>2386</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="C26" s="2">
-        <v>1224</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C27" s="2">
-        <v>883</v>
+        <v>886</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>2412</v>
+        <v>2446</v>
       </c>
       <c r="C28" s="2">
-        <v>20693</v>
+        <v>21050</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1199</v>
+        <v>1219</v>
       </c>
       <c r="C29" s="2">
-        <v>23212</v>
+        <v>23449</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="2">
-        <v>694</v>
-      </c>
-      <c r="C30" s="2">
-        <v>6131</v>
+      <c r="B30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>2096</v>
+        <v>702</v>
       </c>
       <c r="C31" s="2">
-        <v>11949</v>
+        <v>6461</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>712</v>
+        <v>2136</v>
       </c>
       <c r="C32" s="2">
-        <v>9176</v>
+        <v>12132</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>1556</v>
+        <v>735</v>
       </c>
       <c r="C33" s="2">
-        <v>6606</v>
+        <v>9385</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>37</v>
+      <c r="B34" s="2">
+        <v>1573</v>
+      </c>
+      <c r="C34" s="2">
+        <v>6633</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -853,10 +860,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>18989</v>
+        <v>19283</v>
       </c>
       <c r="C36" s="2">
-        <v>173955</v>
+        <v>175376</v>
       </c>
     </row>
   </sheetData>
@@ -907,18 +914,18 @@
       <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C5" s="2">
-        <v>664</v>
+        <v>675</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -929,95 +936,95 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="C7" s="2">
-        <v>5424</v>
+        <v>5715</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C8" s="2">
-        <v>2315</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C9" s="2">
-        <v>1766</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C10" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C11" s="2">
-        <v>758</v>
+        <v>761</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C12" s="2">
-        <v>2273</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="C13" s="2">
-        <v>4693</v>
+        <v>4804</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="C14" s="2">
-        <v>2443</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="2">
@@ -1028,18 +1035,18 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="C16" s="2">
-        <v>2930</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -1050,201 +1057,201 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B18" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C18" s="2">
-        <v>238</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>1282</v>
+        <v>1343</v>
       </c>
       <c r="C19" s="2">
-        <v>6461</v>
+        <v>6929</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>914</v>
+        <v>947</v>
       </c>
       <c r="C20" s="2">
-        <v>5619</v>
+        <v>5745</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1835</v>
+        <v>1913</v>
       </c>
       <c r="C21" s="2">
-        <v>18075</v>
+        <v>18634</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1998</v>
+        <v>2051</v>
       </c>
       <c r="C22" s="2">
-        <v>13472</v>
+        <v>13790</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>676</v>
+        <v>702</v>
       </c>
       <c r="C23" s="2">
-        <v>19766</v>
+        <v>20098</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2966</v>
+        <v>3038</v>
       </c>
       <c r="C24" s="2">
-        <v>31222</v>
+        <v>31474</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="C25" s="2">
-        <v>5194</v>
+        <v>5232</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="C26" s="2">
-        <v>1663</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C27" s="2">
-        <v>1273</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>3500</v>
+        <v>3615</v>
       </c>
       <c r="C28" s="2">
-        <v>31620</v>
+        <v>32793</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1609</v>
+        <v>1675</v>
       </c>
       <c r="C29" s="2">
-        <v>30304</v>
+        <v>30994</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="2">
-        <v>785</v>
-      </c>
-      <c r="C30" s="2">
-        <v>7662</v>
+      <c r="B30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>2600</v>
+        <v>799</v>
       </c>
       <c r="C31" s="2">
-        <v>19101</v>
+        <v>8068</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>828</v>
+        <v>2733</v>
       </c>
       <c r="C32" s="2">
-        <v>10952</v>
+        <v>20349</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>1610</v>
+        <v>868</v>
       </c>
       <c r="C33" s="2">
-        <v>8127</v>
+        <v>11330</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>37</v>
+      <c r="B34" s="2">
+        <v>1657</v>
+      </c>
+      <c r="C34" s="2">
+        <v>8269</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="2">
-        <v>22</v>
-      </c>
-      <c r="C35" s="2">
-        <v>348</v>
+      <c r="B35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -1252,10 +1259,411 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>23582</v>
+        <v>24445</v>
       </c>
       <c r="C36" s="2">
-        <v>235509</v>
+        <v>242749</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="58.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2">
+        <v>51</v>
+      </c>
+      <c r="C5" s="2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>268</v>
+      </c>
+      <c r="C7" s="2">
+        <v>4806</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>111</v>
+      </c>
+      <c r="C8" s="2">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>268</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>55</v>
+      </c>
+      <c r="C10" s="2">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>59</v>
+      </c>
+      <c r="C11" s="2">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>208</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>225</v>
+      </c>
+      <c r="C13" s="2">
+        <v>5340</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>172</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3283</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2">
+        <v>13</v>
+      </c>
+      <c r="C15" s="2">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>250</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="2">
+        <v>24</v>
+      </c>
+      <c r="C18" s="2">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2">
+        <v>1127</v>
+      </c>
+      <c r="C19" s="2">
+        <v>5452</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2">
+        <v>690</v>
+      </c>
+      <c r="C20" s="2">
+        <v>3717</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2">
+        <v>1666</v>
+      </c>
+      <c r="C21" s="2">
+        <v>15412</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1639</v>
+      </c>
+      <c r="C22" s="2">
+        <v>10821</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2">
+        <v>638</v>
+      </c>
+      <c r="C23" s="2">
+        <v>19099</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2">
+        <v>2703</v>
+      </c>
+      <c r="C24" s="2">
+        <v>28520</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2">
+        <v>511</v>
+      </c>
+      <c r="C25" s="2">
+        <v>4148</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2">
+        <v>394</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2">
+        <v>237</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2">
+        <v>3321</v>
+      </c>
+      <c r="C28" s="2">
+        <v>26250</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2">
+        <v>1461</v>
+      </c>
+      <c r="C29" s="2">
+        <v>20164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2">
+        <v>688</v>
+      </c>
+      <c r="C31" s="2">
+        <v>6590</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="2">
+        <v>1394</v>
+      </c>
+      <c r="C32" s="2">
+        <v>8866</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2">
+        <v>803</v>
+      </c>
+      <c r="C33" s="2">
+        <v>9458</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="2">
+        <v>869</v>
+      </c>
+      <c r="C34" s="2">
+        <v>5462</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="2">
+        <v>19861</v>
+      </c>
+      <c r="C36" s="2">
+        <v>190686</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Ausz KonPe KTZH.xlsx
+++ b/KAE Ausz KonPe KTZH.xlsx
@@ -9,12 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="März 2020" sheetId="1" r:id="rId1"/>
     <sheet name="April 2020" sheetId="2" r:id="rId2"/>
     <sheet name="Mai 2020" sheetId="3" r:id="rId3"/>
+    <sheet name="Juni 2020" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="43">
   <si>
     <t>Metriken</t>
   </si>
@@ -152,6 +153,9 @@
   </si>
   <si>
     <t>Mai 2020</t>
+  </si>
+  <si>
+    <t>Juni 2020</t>
   </si>
 </sst>
 </file>
@@ -519,10 +523,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2">
-        <v>642</v>
+        <v>664</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -541,10 +545,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C7" s="2">
-        <v>4431</v>
+        <v>4459</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -552,10 +556,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C8" s="2">
-        <v>2013</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -563,10 +567,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C9" s="2">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -574,10 +578,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -585,10 +589,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -596,10 +600,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C12" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -607,7 +611,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C13" s="2">
         <v>485</v>
@@ -640,10 +644,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C16" s="2">
-        <v>1829</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -673,10 +677,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>887</v>
+        <v>896</v>
       </c>
       <c r="C19" s="2">
-        <v>3571</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -684,10 +688,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="C20" s="2">
-        <v>3506</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -695,10 +699,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1308</v>
+        <v>1316</v>
       </c>
       <c r="C21" s="2">
-        <v>9859</v>
+        <v>9807</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -706,10 +710,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1884</v>
+        <v>1914</v>
       </c>
       <c r="C22" s="2">
-        <v>12064</v>
+        <v>12480</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -717,10 +721,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="C23" s="2">
-        <v>16042</v>
+        <v>16046</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -728,10 +732,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3049</v>
+        <v>3139</v>
       </c>
       <c r="C24" s="2">
-        <v>34093</v>
+        <v>34173</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -739,7 +743,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C25" s="2">
         <v>2416</v>
@@ -750,10 +754,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C26" s="2">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -761,10 +765,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C27" s="2">
-        <v>886</v>
+        <v>897</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -772,10 +776,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>2446</v>
+        <v>2483</v>
       </c>
       <c r="C28" s="2">
-        <v>21050</v>
+        <v>21131</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -783,10 +787,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1219</v>
+        <v>1260</v>
       </c>
       <c r="C29" s="2">
-        <v>23449</v>
+        <v>23504</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -805,10 +809,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>702</v>
+        <v>722</v>
       </c>
       <c r="C31" s="2">
-        <v>6461</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -816,10 +820,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>2136</v>
+        <v>2189</v>
       </c>
       <c r="C32" s="2">
-        <v>12132</v>
+        <v>12292</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -827,10 +831,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>735</v>
+        <v>744</v>
       </c>
       <c r="C33" s="2">
-        <v>9385</v>
+        <v>9895</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -838,10 +842,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>1573</v>
+        <v>1588</v>
       </c>
       <c r="C34" s="2">
-        <v>6633</v>
+        <v>6642</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -860,10 +864,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>19283</v>
+        <v>19638</v>
       </c>
       <c r="C36" s="2">
-        <v>175376</v>
+        <v>176823</v>
       </c>
     </row>
   </sheetData>
@@ -918,10 +922,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C5" s="2">
-        <v>675</v>
+        <v>665</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -940,10 +944,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="C7" s="2">
-        <v>5715</v>
+        <v>5746</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -951,10 +955,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C8" s="2">
-        <v>2316</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -962,10 +966,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C9" s="2">
-        <v>1790</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -973,10 +977,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C10" s="2">
-        <v>485</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -984,10 +988,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C11" s="2">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -995,10 +999,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="C12" s="2">
-        <v>2277</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1006,10 +1010,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C13" s="2">
-        <v>4804</v>
+        <v>5328</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1017,7 +1021,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2">
         <v>2937</v>
@@ -1039,10 +1043,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C16" s="2">
-        <v>2990</v>
+        <v>2998</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1061,10 +1065,10 @@
         <v>33</v>
       </c>
       <c r="B18" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C18" s="2">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1072,10 +1076,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>1343</v>
+        <v>1367</v>
       </c>
       <c r="C19" s="2">
-        <v>6929</v>
+        <v>7027</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1083,10 +1087,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>947</v>
+        <v>973</v>
       </c>
       <c r="C20" s="2">
-        <v>5745</v>
+        <v>5821</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1094,10 +1098,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1913</v>
+        <v>1968</v>
       </c>
       <c r="C21" s="2">
-        <v>18634</v>
+        <v>18923</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1105,10 +1109,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>2051</v>
+        <v>2108</v>
       </c>
       <c r="C22" s="2">
-        <v>13790</v>
+        <v>14585</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1116,10 +1120,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>702</v>
+        <v>729</v>
       </c>
       <c r="C23" s="2">
-        <v>20098</v>
+        <v>20187</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1127,10 +1131,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3038</v>
+        <v>3110</v>
       </c>
       <c r="C24" s="2">
-        <v>31474</v>
+        <v>36302</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1138,10 +1142,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>556</v>
+        <v>569</v>
       </c>
       <c r="C25" s="2">
-        <v>5232</v>
+        <v>5557</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1149,10 +1153,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="C26" s="2">
-        <v>1708</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -1160,10 +1164,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C27" s="2">
-        <v>1289</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -1171,10 +1175,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>3615</v>
+        <v>3689</v>
       </c>
       <c r="C28" s="2">
-        <v>32793</v>
+        <v>33108</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1182,10 +1186,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1675</v>
+        <v>1742</v>
       </c>
       <c r="C29" s="2">
-        <v>30994</v>
+        <v>31552</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1204,10 +1208,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>799</v>
+        <v>823</v>
       </c>
       <c r="C31" s="2">
-        <v>8068</v>
+        <v>8121</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1215,10 +1219,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>2733</v>
+        <v>2859</v>
       </c>
       <c r="C32" s="2">
-        <v>20349</v>
+        <v>21793</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1226,10 +1230,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>868</v>
+        <v>899</v>
       </c>
       <c r="C33" s="2">
-        <v>11330</v>
+        <v>11920</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1237,10 +1241,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>1657</v>
+        <v>1688</v>
       </c>
       <c r="C34" s="2">
-        <v>8269</v>
+        <v>8359</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1259,10 +1263,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>24445</v>
+        <v>25139</v>
       </c>
       <c r="C36" s="2">
-        <v>242749</v>
+        <v>253085</v>
       </c>
     </row>
   </sheetData>
@@ -1319,10 +1323,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C5" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1341,10 +1345,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="C7" s="2">
-        <v>4806</v>
+        <v>5326</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1352,10 +1356,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C8" s="2">
-        <v>724</v>
+        <v>738</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1363,10 +1367,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="C9" s="2">
-        <v>1802</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1374,10 +1378,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C10" s="2">
-        <v>529</v>
+        <v>540</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1385,10 +1389,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C11" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1396,10 +1400,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="C12" s="2">
-        <v>2672</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1407,10 +1411,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="C13" s="2">
-        <v>5340</v>
+        <v>6545</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1418,10 +1422,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2">
-        <v>3283</v>
+        <v>3505</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1440,10 +1444,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="C16" s="2">
-        <v>2655</v>
+        <v>3217</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1462,10 +1466,10 @@
         <v>33</v>
       </c>
       <c r="B18" s="2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C18" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1473,10 +1477,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>1127</v>
+        <v>1179</v>
       </c>
       <c r="C19" s="2">
-        <v>5452</v>
+        <v>5719</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1484,10 +1488,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>690</v>
+        <v>730</v>
       </c>
       <c r="C20" s="2">
-        <v>3717</v>
+        <v>4045</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1495,10 +1499,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1666</v>
+        <v>1762</v>
       </c>
       <c r="C21" s="2">
-        <v>15412</v>
+        <v>16036</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1506,10 +1510,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1639</v>
+        <v>1742</v>
       </c>
       <c r="C22" s="2">
-        <v>10821</v>
+        <v>11678</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1517,10 +1521,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>638</v>
+        <v>683</v>
       </c>
       <c r="C23" s="2">
-        <v>19099</v>
+        <v>19445</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1528,10 +1532,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2703</v>
+        <v>2866</v>
       </c>
       <c r="C24" s="2">
-        <v>28520</v>
+        <v>34265</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1539,10 +1543,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>511</v>
+        <v>547</v>
       </c>
       <c r="C25" s="2">
-        <v>4148</v>
+        <v>5553</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1550,10 +1554,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="C26" s="2">
-        <v>1525</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -1561,10 +1565,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="C27" s="2">
-        <v>1165</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -1572,10 +1576,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>3321</v>
+        <v>3505</v>
       </c>
       <c r="C28" s="2">
-        <v>26250</v>
+        <v>29172</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1583,10 +1587,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1461</v>
+        <v>1581</v>
       </c>
       <c r="C29" s="2">
-        <v>20164</v>
+        <v>20975</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1605,10 +1609,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>688</v>
+        <v>726</v>
       </c>
       <c r="C31" s="2">
-        <v>6590</v>
+        <v>6834</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1616,10 +1620,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>1394</v>
+        <v>1508</v>
       </c>
       <c r="C32" s="2">
-        <v>8866</v>
+        <v>10021</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1627,10 +1631,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>803</v>
+        <v>875</v>
       </c>
       <c r="C33" s="2">
-        <v>9458</v>
+        <v>11449</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1638,10 +1642,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>869</v>
+        <v>930</v>
       </c>
       <c r="C34" s="2">
-        <v>5462</v>
+        <v>5634</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1660,10 +1664,411 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>19861</v>
+        <v>21120</v>
       </c>
       <c r="C36" s="2">
-        <v>190686</v>
+        <v>210799</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="58.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2">
+        <v>23</v>
+      </c>
+      <c r="C5" s="2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>178</v>
+      </c>
+      <c r="C7" s="2">
+        <v>3579</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>57</v>
+      </c>
+      <c r="C8" s="2">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>197</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>41</v>
+      </c>
+      <c r="C10" s="2">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>43</v>
+      </c>
+      <c r="C11" s="2">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>174</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>208</v>
+      </c>
+      <c r="C13" s="2">
+        <v>5576</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>150</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>132</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2">
+        <v>719</v>
+      </c>
+      <c r="C19" s="2">
+        <v>2747</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2">
+        <v>375</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2">
+        <v>1093</v>
+      </c>
+      <c r="C21" s="2">
+        <v>10600</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2">
+        <v>758</v>
+      </c>
+      <c r="C22" s="2">
+        <v>5099</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2">
+        <v>471</v>
+      </c>
+      <c r="C23" s="2">
+        <v>29695</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2">
+        <v>2016</v>
+      </c>
+      <c r="C24" s="2">
+        <v>25225</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2">
+        <v>327</v>
+      </c>
+      <c r="C25" s="2">
+        <v>3764</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2">
+        <v>228</v>
+      </c>
+      <c r="C26" s="2">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2">
+        <v>134</v>
+      </c>
+      <c r="C27" s="2">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2">
+        <v>1972</v>
+      </c>
+      <c r="C28" s="2">
+        <v>17574</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2">
+        <v>1040</v>
+      </c>
+      <c r="C29" s="2">
+        <v>15258</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2">
+        <v>326</v>
+      </c>
+      <c r="C31" s="2">
+        <v>3394</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="2">
+        <v>596</v>
+      </c>
+      <c r="C32" s="2">
+        <v>4005</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2">
+        <v>485</v>
+      </c>
+      <c r="C33" s="2">
+        <v>6101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="2">
+        <v>612</v>
+      </c>
+      <c r="C34" s="2">
+        <v>3454</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="2">
+        <v>12401</v>
+      </c>
+      <c r="C36" s="2">
+        <v>150783</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Ausz KonPe KTZH.xlsx
+++ b/KAE Ausz KonPe KTZH.xlsx
@@ -9,13 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="März 2020" sheetId="1" r:id="rId1"/>
     <sheet name="April 2020" sheetId="2" r:id="rId2"/>
     <sheet name="Mai 2020" sheetId="3" r:id="rId3"/>
     <sheet name="Juni 2020" sheetId="4" r:id="rId4"/>
+    <sheet name="Juli 2020" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="44">
   <si>
     <t>Metriken</t>
   </si>
@@ -156,6 +157,9 @@
   </si>
   <si>
     <t>Juni 2020</t>
+  </si>
+  <si>
+    <t>Juli 2020</t>
   </si>
 </sst>
 </file>
@@ -611,7 +615,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C13" s="2">
         <v>485</v>
@@ -677,10 +681,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="C19" s="2">
-        <v>3631</v>
+        <v>3601</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -699,10 +703,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1316</v>
+        <v>1322</v>
       </c>
       <c r="C21" s="2">
-        <v>9807</v>
+        <v>10013</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -713,7 +717,7 @@
         <v>1914</v>
       </c>
       <c r="C22" s="2">
-        <v>12480</v>
+        <v>12230</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -721,10 +725,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="C23" s="2">
-        <v>16046</v>
+        <v>16047</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -732,10 +736,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3139</v>
+        <v>3149</v>
       </c>
       <c r="C24" s="2">
-        <v>34173</v>
+        <v>34162</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -754,7 +758,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C26" s="2">
         <v>1249</v>
@@ -776,10 +780,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>2483</v>
+        <v>2495</v>
       </c>
       <c r="C28" s="2">
-        <v>21131</v>
+        <v>20975</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -787,10 +791,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1260</v>
+        <v>1269</v>
       </c>
       <c r="C29" s="2">
-        <v>23504</v>
+        <v>23520</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -809,7 +813,7 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C31" s="2">
         <v>6500</v>
@@ -820,10 +824,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>2189</v>
+        <v>2193</v>
       </c>
       <c r="C32" s="2">
-        <v>12292</v>
+        <v>12295</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -831,7 +835,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="C33" s="2">
         <v>9895</v>
@@ -842,10 +846,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>1588</v>
+        <v>1591</v>
       </c>
       <c r="C34" s="2">
-        <v>6642</v>
+        <v>6644</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -864,10 +868,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>19638</v>
+        <v>19702</v>
       </c>
       <c r="C36" s="2">
-        <v>176823</v>
+        <v>176604</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +948,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C7" s="2">
         <v>5746</v>
@@ -999,10 +1003,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C12" s="2">
-        <v>2297</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1010,10 +1014,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C13" s="2">
-        <v>5328</v>
+        <v>5438</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1076,10 +1080,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>1367</v>
+        <v>1372</v>
       </c>
       <c r="C19" s="2">
-        <v>7027</v>
+        <v>6994</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1087,10 +1091,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="C20" s="2">
-        <v>5821</v>
+        <v>5844</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1098,10 +1102,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1968</v>
+        <v>1984</v>
       </c>
       <c r="C21" s="2">
-        <v>18923</v>
+        <v>19341</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1109,10 +1113,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="C22" s="2">
-        <v>14585</v>
+        <v>14351</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1120,10 +1124,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="C23" s="2">
-        <v>20187</v>
+        <v>20189</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1131,10 +1135,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3110</v>
+        <v>3123</v>
       </c>
       <c r="C24" s="2">
-        <v>36302</v>
+        <v>36292</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1142,10 +1146,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C25" s="2">
-        <v>5557</v>
+        <v>5561</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1153,7 +1157,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C26" s="2">
         <v>1718</v>
@@ -1175,10 +1179,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>3689</v>
+        <v>3704</v>
       </c>
       <c r="C28" s="2">
-        <v>33108</v>
+        <v>33011</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1186,10 +1190,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1742</v>
+        <v>1750</v>
       </c>
       <c r="C29" s="2">
-        <v>31552</v>
+        <v>31558</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1208,10 +1212,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="C31" s="2">
-        <v>8121</v>
+        <v>8137</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1219,10 +1223,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>2859</v>
+        <v>2872</v>
       </c>
       <c r="C32" s="2">
-        <v>21793</v>
+        <v>21892</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1230,10 +1234,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="C33" s="2">
-        <v>11920</v>
+        <v>11950</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1241,10 +1245,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>1688</v>
+        <v>1694</v>
       </c>
       <c r="C34" s="2">
-        <v>8359</v>
+        <v>8379</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1263,10 +1267,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>25139</v>
+        <v>25248</v>
       </c>
       <c r="C36" s="2">
-        <v>253085</v>
+        <v>253494</v>
       </c>
     </row>
   </sheetData>
@@ -1400,10 +1404,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C12" s="2">
-        <v>2990</v>
+        <v>2987</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1411,7 +1415,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C13" s="2">
         <v>6545</v>
@@ -1444,7 +1448,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C16" s="2">
         <v>3217</v>
@@ -1477,10 +1481,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>1179</v>
+        <v>1189</v>
       </c>
       <c r="C19" s="2">
-        <v>5719</v>
+        <v>5697</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1488,10 +1492,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="C20" s="2">
-        <v>4045</v>
+        <v>4053</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1499,10 +1503,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1762</v>
+        <v>1780</v>
       </c>
       <c r="C21" s="2">
-        <v>16036</v>
+        <v>16409</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1510,10 +1514,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1742</v>
+        <v>1747</v>
       </c>
       <c r="C22" s="2">
-        <v>11678</v>
+        <v>11897</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1521,10 +1525,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="C23" s="2">
-        <v>19445</v>
+        <v>19446</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1532,10 +1536,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2866</v>
+        <v>2881</v>
       </c>
       <c r="C24" s="2">
-        <v>34265</v>
+        <v>34336</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1543,10 +1547,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C25" s="2">
-        <v>5553</v>
+        <v>5573</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1554,7 +1558,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C26" s="2">
         <v>1660</v>
@@ -1565,10 +1569,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C27" s="2">
-        <v>1220</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -1576,10 +1580,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>3505</v>
+        <v>3525</v>
       </c>
       <c r="C28" s="2">
-        <v>29172</v>
+        <v>29150</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1587,10 +1591,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1581</v>
+        <v>1593</v>
       </c>
       <c r="C29" s="2">
-        <v>20975</v>
+        <v>20962</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1609,10 +1613,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="C31" s="2">
-        <v>6834</v>
+        <v>6849</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1620,10 +1624,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>1508</v>
+        <v>1516</v>
       </c>
       <c r="C32" s="2">
-        <v>10021</v>
+        <v>10035</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1631,10 +1635,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="C33" s="2">
-        <v>11449</v>
+        <v>11457</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1642,10 +1646,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="C34" s="2">
-        <v>5634</v>
+        <v>5683</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1664,10 +1668,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>21120</v>
+        <v>21246</v>
       </c>
       <c r="C36" s="2">
-        <v>210799</v>
+        <v>211525</v>
       </c>
     </row>
   </sheetData>
@@ -1746,10 +1750,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C7" s="2">
-        <v>3579</v>
+        <v>3602</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1757,10 +1761,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C8" s="2">
-        <v>463</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1768,10 +1772,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C9" s="2">
-        <v>1578</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1779,10 +1783,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" s="2">
-        <v>370</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1790,10 +1794,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" s="2">
-        <v>425</v>
+        <v>463</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -1812,10 +1816,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C13" s="2">
-        <v>5576</v>
+        <v>5575</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1823,10 +1827,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C14" s="2">
-        <v>2880</v>
+        <v>2881</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1845,10 +1849,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C16" s="2">
-        <v>2258</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1878,10 +1882,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>719</v>
+        <v>729</v>
       </c>
       <c r="C19" s="2">
-        <v>2747</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1889,10 +1893,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="C20" s="2">
-        <v>1501</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1900,10 +1904,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1093</v>
+        <v>1112</v>
       </c>
       <c r="C21" s="2">
-        <v>10600</v>
+        <v>10946</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1911,10 +1915,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>758</v>
+        <v>771</v>
       </c>
       <c r="C22" s="2">
-        <v>5099</v>
+        <v>5544</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1922,10 +1926,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="C23" s="2">
-        <v>29695</v>
+        <v>29694</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1933,10 +1937,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2016</v>
+        <v>2058</v>
       </c>
       <c r="C24" s="2">
-        <v>25225</v>
+        <v>25300</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1944,10 +1948,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="C25" s="2">
-        <v>3764</v>
+        <v>3776</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1955,7 +1959,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C26" s="2">
         <v>896</v>
@@ -1966,10 +1970,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C27" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -1977,10 +1981,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1972</v>
+        <v>2009</v>
       </c>
       <c r="C28" s="2">
-        <v>17574</v>
+        <v>17459</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1988,10 +1992,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1040</v>
+        <v>1062</v>
       </c>
       <c r="C29" s="2">
-        <v>15258</v>
+        <v>15311</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2010,10 +2014,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="C31" s="2">
-        <v>3394</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2021,10 +2025,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>596</v>
+        <v>606</v>
       </c>
       <c r="C32" s="2">
-        <v>4005</v>
+        <v>4007</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -2032,10 +2036,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="C33" s="2">
-        <v>6101</v>
+        <v>6109</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2043,10 +2047,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>612</v>
+        <v>629</v>
       </c>
       <c r="C34" s="2">
-        <v>3454</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2065,10 +2069,411 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>12401</v>
+        <v>12641</v>
       </c>
       <c r="C36" s="2">
-        <v>150783</v>
+        <v>151774</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="58.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>124</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2577</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>46</v>
+      </c>
+      <c r="C8" s="2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>157</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>28</v>
+      </c>
+      <c r="C11" s="2">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>145</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>157</v>
+      </c>
+      <c r="C13" s="2">
+        <v>3752</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>130</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2720</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2">
+        <v>11</v>
+      </c>
+      <c r="C15" s="2">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>100</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2">
+        <v>555</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2">
+        <v>287</v>
+      </c>
+      <c r="C20" s="2">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2">
+        <v>822</v>
+      </c>
+      <c r="C21" s="2">
+        <v>7923</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2">
+        <v>561</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3536</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2">
+        <v>408</v>
+      </c>
+      <c r="C23" s="2">
+        <v>16072</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1604</v>
+      </c>
+      <c r="C24" s="2">
+        <v>15995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2">
+        <v>246</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2703</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2">
+        <v>180</v>
+      </c>
+      <c r="C26" s="2">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2">
+        <v>89</v>
+      </c>
+      <c r="C27" s="2">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2">
+        <v>1397</v>
+      </c>
+      <c r="C28" s="2">
+        <v>12363</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2">
+        <v>879</v>
+      </c>
+      <c r="C29" s="2">
+        <v>10897</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2">
+        <v>185</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="2">
+        <v>383</v>
+      </c>
+      <c r="C32" s="2">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2">
+        <v>318</v>
+      </c>
+      <c r="C33" s="2">
+        <v>2934</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="2">
+        <v>468</v>
+      </c>
+      <c r="C34" s="2">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="2">
+        <v>9346</v>
+      </c>
+      <c r="C36" s="2">
+        <v>98712</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Ausz KonPe KTZH.xlsx
+++ b/KAE Ausz KonPe KTZH.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="März 2020" sheetId="1" r:id="rId1"/>
@@ -17,6 +17,7 @@
     <sheet name="Mai 2020" sheetId="3" r:id="rId3"/>
     <sheet name="Juni 2020" sheetId="4" r:id="rId4"/>
     <sheet name="Juli 2020" sheetId="5" r:id="rId5"/>
+    <sheet name="August 2020" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="45">
   <si>
     <t>Metriken</t>
   </si>
@@ -160,6 +161,9 @@
   </si>
   <si>
     <t>Juli 2020</t>
+  </si>
+  <si>
+    <t>August 2020</t>
   </si>
 </sst>
 </file>
@@ -527,10 +531,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2">
-        <v>664</v>
+        <v>667</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -582,7 +586,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" s="2">
         <v>212</v>
@@ -604,7 +608,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C12" s="2">
         <v>506</v>
@@ -681,10 +685,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="C19" s="2">
-        <v>3601</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -692,7 +696,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C20" s="2">
         <v>3517</v>
@@ -703,7 +707,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="C21" s="2">
         <v>10013</v>
@@ -714,10 +718,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C22" s="2">
-        <v>12230</v>
+        <v>12243</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -725,10 +729,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C23" s="2">
-        <v>16047</v>
+        <v>16051</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -736,10 +740,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3149</v>
+        <v>3172</v>
       </c>
       <c r="C24" s="2">
-        <v>34162</v>
+        <v>34177</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -769,7 +773,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C27" s="2">
         <v>897</v>
@@ -780,10 +784,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>2495</v>
+        <v>2500</v>
       </c>
       <c r="C28" s="2">
-        <v>20975</v>
+        <v>20972</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -791,7 +795,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1269</v>
+        <v>1280</v>
       </c>
       <c r="C29" s="2">
         <v>23520</v>
@@ -824,10 +828,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>2193</v>
+        <v>2198</v>
       </c>
       <c r="C32" s="2">
-        <v>12295</v>
+        <v>12349</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -835,7 +839,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C33" s="2">
         <v>9895</v>
@@ -846,10 +850,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="C34" s="2">
-        <v>6644</v>
+        <v>6647</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -868,10 +872,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>19702</v>
+        <v>19768</v>
       </c>
       <c r="C36" s="2">
-        <v>176604</v>
+        <v>176685</v>
       </c>
     </row>
   </sheetData>
@@ -926,10 +930,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C5" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -948,7 +952,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C7" s="2">
         <v>5746</v>
@@ -981,7 +985,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C10" s="2">
         <v>492</v>
@@ -1003,7 +1007,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C12" s="2">
         <v>2352</v>
@@ -1025,10 +1029,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C14" s="2">
-        <v>2937</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1047,10 +1051,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C16" s="2">
-        <v>2998</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1080,10 +1084,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>1372</v>
+        <v>1380</v>
       </c>
       <c r="C19" s="2">
-        <v>6994</v>
+        <v>7025</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1091,7 +1095,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="C20" s="2">
         <v>5844</v>
@@ -1102,10 +1106,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1984</v>
+        <v>1987</v>
       </c>
       <c r="C21" s="2">
-        <v>19341</v>
+        <v>19338</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1113,10 +1117,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>2110</v>
+        <v>2117</v>
       </c>
       <c r="C22" s="2">
-        <v>14351</v>
+        <v>14380</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1124,10 +1128,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="C23" s="2">
-        <v>20189</v>
+        <v>20193</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1135,10 +1139,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3123</v>
+        <v>3150</v>
       </c>
       <c r="C24" s="2">
-        <v>36292</v>
+        <v>36318</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1157,10 +1161,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C26" s="2">
-        <v>1718</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -1179,10 +1183,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>3704</v>
+        <v>3719</v>
       </c>
       <c r="C28" s="2">
-        <v>33011</v>
+        <v>32999</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1190,10 +1194,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1750</v>
+        <v>1766</v>
       </c>
       <c r="C29" s="2">
-        <v>31558</v>
+        <v>31688</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1212,10 +1216,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C31" s="2">
-        <v>8137</v>
+        <v>8139</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1223,10 +1227,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>2872</v>
+        <v>2886</v>
       </c>
       <c r="C32" s="2">
-        <v>21892</v>
+        <v>22015</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1234,7 +1238,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C33" s="2">
         <v>11950</v>
@@ -1245,10 +1249,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="C34" s="2">
-        <v>8379</v>
+        <v>8383</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1267,10 +1271,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>25248</v>
+        <v>25367</v>
       </c>
       <c r="C36" s="2">
-        <v>253494</v>
+        <v>253847</v>
       </c>
     </row>
   </sheetData>
@@ -1349,7 +1353,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C7" s="2">
         <v>5326</v>
@@ -1371,7 +1375,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C9" s="2">
         <v>1985</v>
@@ -1382,7 +1386,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" s="2">
         <v>540</v>
@@ -1426,10 +1430,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C14" s="2">
-        <v>3505</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1437,10 +1441,10 @@
         <v>32</v>
       </c>
       <c r="B15" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C15" s="2">
-        <v>679</v>
+        <v>709</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1448,10 +1452,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C16" s="2">
-        <v>3217</v>
+        <v>3218</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1481,10 +1485,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="C19" s="2">
-        <v>5697</v>
+        <v>5686</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1492,10 +1496,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C20" s="2">
-        <v>4053</v>
+        <v>4054</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1503,10 +1507,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1780</v>
+        <v>1784</v>
       </c>
       <c r="C21" s="2">
-        <v>16409</v>
+        <v>16406</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1514,10 +1518,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1747</v>
+        <v>1755</v>
       </c>
       <c r="C22" s="2">
-        <v>11897</v>
+        <v>11923</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1525,10 +1529,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="C23" s="2">
-        <v>19446</v>
+        <v>19454</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1536,10 +1540,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2881</v>
+        <v>2910</v>
       </c>
       <c r="C24" s="2">
-        <v>34336</v>
+        <v>34387</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1547,10 +1551,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C25" s="2">
-        <v>5573</v>
+        <v>5575</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1558,10 +1562,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C26" s="2">
-        <v>1660</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -1580,10 +1584,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>3525</v>
+        <v>3558</v>
       </c>
       <c r="C28" s="2">
-        <v>29150</v>
+        <v>29295</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1591,10 +1595,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1593</v>
+        <v>1609</v>
       </c>
       <c r="C29" s="2">
-        <v>20962</v>
+        <v>21132</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1613,10 +1617,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="C31" s="2">
-        <v>6849</v>
+        <v>6855</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1624,10 +1628,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>1516</v>
+        <v>1522</v>
       </c>
       <c r="C32" s="2">
-        <v>10035</v>
+        <v>10067</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1635,10 +1639,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C33" s="2">
-        <v>11457</v>
+        <v>11462</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1646,10 +1650,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="C34" s="2">
-        <v>5683</v>
+        <v>5691</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1668,10 +1672,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>21246</v>
+        <v>21386</v>
       </c>
       <c r="C36" s="2">
-        <v>211525</v>
+        <v>212045</v>
       </c>
     </row>
   </sheetData>
@@ -1728,7 +1732,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="2">
         <v>112</v>
@@ -1750,10 +1754,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C7" s="2">
-        <v>3602</v>
+        <v>3673</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1761,7 +1765,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C8" s="2">
         <v>486</v>
@@ -1772,10 +1776,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="C9" s="2">
-        <v>1574</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1783,10 +1787,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C10" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1805,7 +1809,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C12" s="2">
         <v>2457</v>
@@ -1816,7 +1820,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C13" s="2">
         <v>5575</v>
@@ -1827,10 +1831,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C14" s="2">
-        <v>2881</v>
+        <v>2889</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1838,10 +1842,10 @@
         <v>32</v>
       </c>
       <c r="B15" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C15" s="2">
-        <v>613</v>
+        <v>664</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -1849,10 +1853,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2">
-        <v>2262</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1882,10 +1886,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>729</v>
+        <v>741</v>
       </c>
       <c r="C19" s="2">
-        <v>2753</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1893,10 +1897,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C20" s="2">
-        <v>1498</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1904,10 +1908,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1112</v>
+        <v>1119</v>
       </c>
       <c r="C21" s="2">
-        <v>10946</v>
+        <v>11153</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1915,10 +1919,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="C22" s="2">
-        <v>5544</v>
+        <v>5553</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1926,10 +1930,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>480</v>
+        <v>493</v>
       </c>
       <c r="C23" s="2">
-        <v>29694</v>
+        <v>29676</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1937,10 +1941,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2058</v>
+        <v>2093</v>
       </c>
       <c r="C24" s="2">
-        <v>25300</v>
+        <v>25319</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1948,10 +1952,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="C25" s="2">
-        <v>3776</v>
+        <v>3779</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1959,10 +1963,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C26" s="2">
-        <v>896</v>
+        <v>899</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -1970,10 +1974,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C27" s="2">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -1981,10 +1985,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>2009</v>
+        <v>2038</v>
       </c>
       <c r="C28" s="2">
-        <v>17459</v>
+        <v>17506</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1992,10 +1996,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1062</v>
+        <v>1087</v>
       </c>
       <c r="C29" s="2">
-        <v>15311</v>
+        <v>15455</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2014,10 +2018,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C31" s="2">
-        <v>3397</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2025,10 +2029,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="C32" s="2">
-        <v>4007</v>
+        <v>4019</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -2036,10 +2040,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="C33" s="2">
-        <v>6109</v>
+        <v>6116</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2047,10 +2051,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>629</v>
+        <v>639</v>
       </c>
       <c r="C34" s="2">
-        <v>3495</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2069,10 +2073,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>12641</v>
+        <v>12857</v>
       </c>
       <c r="C36" s="2">
-        <v>151774</v>
+        <v>152403</v>
       </c>
     </row>
   </sheetData>
@@ -2151,10 +2155,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C7" s="2">
-        <v>2577</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2162,10 +2166,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C8" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -2173,10 +2177,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C9" s="2">
-        <v>1204</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2184,10 +2188,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" s="2">
-        <v>262</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2206,10 +2210,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C12" s="2">
-        <v>1904</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -2228,10 +2232,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2">
-        <v>2720</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2239,10 +2243,10 @@
         <v>32</v>
       </c>
       <c r="B15" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C15" s="2">
-        <v>612</v>
+        <v>634</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -2250,10 +2254,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C16" s="2">
-        <v>1852</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2283,10 +2287,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>555</v>
+        <v>566</v>
       </c>
       <c r="C19" s="2">
-        <v>1788</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2294,10 +2298,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="C20" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2305,10 +2309,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="C21" s="2">
-        <v>7923</v>
+        <v>7937</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2316,10 +2320,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C22" s="2">
-        <v>3536</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2327,10 +2331,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="C23" s="2">
-        <v>16072</v>
+        <v>16534</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2338,10 +2342,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1604</v>
+        <v>1637</v>
       </c>
       <c r="C24" s="2">
-        <v>15995</v>
+        <v>16039</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2349,10 +2353,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C25" s="2">
-        <v>2703</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -2360,10 +2364,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C26" s="2">
-        <v>635</v>
+        <v>641</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -2371,10 +2375,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C27" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -2382,10 +2386,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1397</v>
+        <v>1446</v>
       </c>
       <c r="C28" s="2">
-        <v>12363</v>
+        <v>12454</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2393,10 +2397,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>879</v>
+        <v>903</v>
       </c>
       <c r="C29" s="2">
-        <v>10897</v>
+        <v>10946</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2415,10 +2419,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C31" s="2">
-        <v>1834</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2426,10 +2430,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="C32" s="2">
-        <v>2196</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -2437,10 +2441,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="C33" s="2">
-        <v>2934</v>
+        <v>2946</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2448,10 +2452,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="C34" s="2">
-        <v>2508</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2470,10 +2474,411 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>9346</v>
+        <v>9582</v>
       </c>
       <c r="C36" s="2">
-        <v>98712</v>
+        <v>99571</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="58.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>102</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>40</v>
+      </c>
+      <c r="C8" s="2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>132</v>
+      </c>
+      <c r="C9" s="2">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>24</v>
+      </c>
+      <c r="C10" s="2">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>26</v>
+      </c>
+      <c r="C11" s="2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>124</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>151</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>105</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>91</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2">
+        <v>450</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2">
+        <v>235</v>
+      </c>
+      <c r="C20" s="2">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2">
+        <v>688</v>
+      </c>
+      <c r="C21" s="2">
+        <v>6604</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2">
+        <v>466</v>
+      </c>
+      <c r="C22" s="2">
+        <v>2859</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2">
+        <v>361</v>
+      </c>
+      <c r="C23" s="2">
+        <v>16144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1404</v>
+      </c>
+      <c r="C24" s="2">
+        <v>13908</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2">
+        <v>207</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2">
+        <v>141</v>
+      </c>
+      <c r="C26" s="2">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2">
+        <v>80</v>
+      </c>
+      <c r="C27" s="2">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2">
+        <v>1206</v>
+      </c>
+      <c r="C28" s="2">
+        <v>10125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2">
+        <v>811</v>
+      </c>
+      <c r="C29" s="2">
+        <v>9589</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2">
+        <v>147</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="2">
+        <v>310</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2">
+        <v>277</v>
+      </c>
+      <c r="C33" s="2">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="2">
+        <v>400</v>
+      </c>
+      <c r="C34" s="2">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="2">
+        <v>8014</v>
+      </c>
+      <c r="C36" s="2">
+        <v>84842</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Ausz KonPe KTZH.xlsx
+++ b/KAE Ausz KonPe KTZH.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\STAT\01_Post\Schlaepfer\covid19monitoring\economy_AWA_private\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Werkstatt\Amtsleitung\Monitoring Covid19\Produktion\Versand\Externe\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="März 2020" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,8 @@
     <sheet name="Juni 2020" sheetId="4" r:id="rId4"/>
     <sheet name="Juli 2020" sheetId="5" r:id="rId5"/>
     <sheet name="August 2020" sheetId="6" r:id="rId6"/>
+    <sheet name="September 2020" sheetId="7" r:id="rId7"/>
+    <sheet name="Oktober 2020" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="47">
   <si>
     <t>Metriken</t>
   </si>
@@ -163,13 +165,19 @@
     <t>Juli 2020</t>
   </si>
   <si>
+    <t>September 2020</t>
+  </si>
+  <si>
     <t>August 2020</t>
+  </si>
+  <si>
+    <t>Oktober 2020</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -229,7 +237,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -531,7 +539,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2">
         <v>667</v>
@@ -553,10 +561,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C7" s="2">
-        <v>4459</v>
+        <v>4461</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -575,7 +583,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C9" s="2">
         <v>901</v>
@@ -608,7 +616,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C12" s="2">
         <v>506</v>
@@ -619,10 +627,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C13" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -652,7 +660,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C16" s="2">
         <v>1832</v>
@@ -685,10 +693,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C19" s="2">
-        <v>3593</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -696,10 +704,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="C20" s="2">
-        <v>3517</v>
+        <v>3537</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -707,10 +715,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1324</v>
+        <v>1330</v>
       </c>
       <c r="C21" s="2">
-        <v>10013</v>
+        <v>10027</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -718,10 +726,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1918</v>
+        <v>1925</v>
       </c>
       <c r="C22" s="2">
-        <v>12243</v>
+        <v>12235</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -729,10 +737,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C23" s="2">
-        <v>16051</v>
+        <v>16050</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -740,10 +748,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3172</v>
+        <v>3192</v>
       </c>
       <c r="C24" s="2">
-        <v>34177</v>
+        <v>34202</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -751,10 +759,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C25" s="2">
-        <v>2416</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -773,10 +781,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C27" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -784,10 +792,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>2500</v>
+        <v>2505</v>
       </c>
       <c r="C28" s="2">
-        <v>20972</v>
+        <v>20973</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -795,10 +803,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1280</v>
+        <v>1289</v>
       </c>
       <c r="C29" s="2">
-        <v>23520</v>
+        <v>23542</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -817,7 +825,7 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C31" s="2">
         <v>6500</v>
@@ -828,10 +836,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>2198</v>
+        <v>2202</v>
       </c>
       <c r="C32" s="2">
-        <v>12349</v>
+        <v>12359</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -839,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>749</v>
+        <v>758</v>
       </c>
       <c r="C33" s="2">
-        <v>9895</v>
+        <v>9907</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -850,10 +858,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="C34" s="2">
-        <v>6647</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -872,10 +880,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>19768</v>
+        <v>19850</v>
       </c>
       <c r="C36" s="2">
-        <v>176685</v>
+        <v>176784</v>
       </c>
     </row>
   </sheetData>
@@ -930,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C5" s="2">
         <v>666</v>
@@ -952,10 +960,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C7" s="2">
-        <v>5746</v>
+        <v>5761</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -963,10 +971,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C8" s="2">
-        <v>2320</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -974,7 +982,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C9" s="2">
         <v>1966</v>
@@ -1007,7 +1015,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C12" s="2">
         <v>2352</v>
@@ -1018,10 +1026,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="C13" s="2">
-        <v>5438</v>
+        <v>5497</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1029,7 +1037,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2">
         <v>2951</v>
@@ -1051,7 +1059,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C16" s="2">
         <v>2999</v>
@@ -1073,10 +1081,10 @@
         <v>33</v>
       </c>
       <c r="B18" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C18" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1084,10 +1092,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="C19" s="2">
-        <v>7025</v>
+        <v>7019</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1095,10 +1103,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C20" s="2">
-        <v>5844</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1106,10 +1114,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1987</v>
+        <v>2000</v>
       </c>
       <c r="C21" s="2">
-        <v>19338</v>
+        <v>19346</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1117,10 +1125,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>2117</v>
+        <v>2127</v>
       </c>
       <c r="C22" s="2">
-        <v>14380</v>
+        <v>14377</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1128,10 +1136,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C23" s="2">
-        <v>20193</v>
+        <v>20191</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1139,10 +1147,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3150</v>
+        <v>3168</v>
       </c>
       <c r="C24" s="2">
-        <v>36318</v>
+        <v>36146</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1150,10 +1158,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C25" s="2">
-        <v>5561</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1161,10 +1169,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C26" s="2">
-        <v>1721</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -1172,7 +1180,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C27" s="2">
         <v>1297</v>
@@ -1183,10 +1191,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>3719</v>
+        <v>3728</v>
       </c>
       <c r="C28" s="2">
-        <v>32999</v>
+        <v>33026</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1194,10 +1202,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1766</v>
+        <v>1775</v>
       </c>
       <c r="C29" s="2">
-        <v>31688</v>
+        <v>31695</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1216,10 +1224,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="C31" s="2">
-        <v>8139</v>
+        <v>8116</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1227,10 +1235,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>2886</v>
+        <v>2898</v>
       </c>
       <c r="C32" s="2">
-        <v>22015</v>
+        <v>22026</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1238,10 +1246,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="C33" s="2">
-        <v>11950</v>
+        <v>11949</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1249,10 +1257,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>1697</v>
+        <v>1701</v>
       </c>
       <c r="C34" s="2">
-        <v>8383</v>
+        <v>8389</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1271,10 +1279,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>25367</v>
+        <v>25489</v>
       </c>
       <c r="C36" s="2">
-        <v>253847</v>
+        <v>253836</v>
       </c>
     </row>
   </sheetData>
@@ -1331,7 +1339,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C5" s="2">
         <v>271</v>
@@ -1353,7 +1361,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C7" s="2">
         <v>5326</v>
@@ -1364,10 +1372,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2">
-        <v>738</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1375,7 +1383,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C9" s="2">
         <v>1985</v>
@@ -1408,7 +1416,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C12" s="2">
         <v>2987</v>
@@ -1419,10 +1427,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="C13" s="2">
-        <v>6545</v>
+        <v>6548</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1430,7 +1438,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C14" s="2">
         <v>3516</v>
@@ -1452,7 +1460,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C16" s="2">
         <v>3218</v>
@@ -1474,10 +1482,10 @@
         <v>33</v>
       </c>
       <c r="B18" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C18" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -1485,10 +1493,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="C19" s="2">
-        <v>5686</v>
+        <v>5682</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1496,10 +1504,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="C20" s="2">
-        <v>4054</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1507,10 +1515,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1784</v>
+        <v>1799</v>
       </c>
       <c r="C21" s="2">
-        <v>16406</v>
+        <v>17738</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1518,10 +1526,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1755</v>
+        <v>1766</v>
       </c>
       <c r="C22" s="2">
-        <v>11923</v>
+        <v>11930</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1529,10 +1537,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="C23" s="2">
-        <v>19454</v>
+        <v>19456</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1540,10 +1548,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2910</v>
+        <v>2926</v>
       </c>
       <c r="C24" s="2">
-        <v>34387</v>
+        <v>34406</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1551,10 +1559,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C25" s="2">
-        <v>5575</v>
+        <v>5572</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1562,10 +1570,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C26" s="2">
-        <v>1663</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -1573,7 +1581,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2">
         <v>1228</v>
@@ -1584,10 +1592,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>3558</v>
+        <v>3578</v>
       </c>
       <c r="C28" s="2">
-        <v>29295</v>
+        <v>29317</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1595,10 +1603,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1609</v>
+        <v>1618</v>
       </c>
       <c r="C29" s="2">
-        <v>21132</v>
+        <v>21130</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1617,10 +1625,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="C31" s="2">
-        <v>6855</v>
+        <v>6868</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1628,10 +1636,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>1522</v>
+        <v>1528</v>
       </c>
       <c r="C32" s="2">
-        <v>10067</v>
+        <v>10078</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1639,10 +1647,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="C33" s="2">
-        <v>11462</v>
+        <v>11440</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1650,10 +1658,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C34" s="2">
-        <v>5691</v>
+        <v>5695</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1672,10 +1680,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>21386</v>
+        <v>21515</v>
       </c>
       <c r="C36" s="2">
-        <v>212045</v>
+        <v>214970</v>
       </c>
     </row>
   </sheetData>
@@ -1732,7 +1740,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" s="2">
         <v>112</v>
@@ -1754,7 +1762,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C7" s="2">
         <v>3673</v>
@@ -1765,10 +1773,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C8" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1776,10 +1784,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C9" s="2">
-        <v>1567</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1820,10 +1828,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="C13" s="2">
-        <v>5575</v>
+        <v>5576</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1831,10 +1839,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C14" s="2">
-        <v>2889</v>
+        <v>2893</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1853,10 +1861,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2">
-        <v>2260</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1886,10 +1894,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="C19" s="2">
-        <v>2752</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1897,10 +1905,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C20" s="2">
-        <v>1491</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1908,10 +1916,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1119</v>
+        <v>1136</v>
       </c>
       <c r="C21" s="2">
-        <v>11153</v>
+        <v>11148</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1919,10 +1927,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>779</v>
+        <v>790</v>
       </c>
       <c r="C22" s="2">
-        <v>5553</v>
+        <v>5558</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1930,10 +1938,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="C23" s="2">
-        <v>29676</v>
+        <v>29699</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1941,10 +1949,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2093</v>
+        <v>2114</v>
       </c>
       <c r="C24" s="2">
-        <v>25319</v>
+        <v>25341</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1952,10 +1960,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C25" s="2">
-        <v>3779</v>
+        <v>3774</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1963,10 +1971,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C26" s="2">
-        <v>899</v>
+        <v>903</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -1974,10 +1982,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C27" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -1985,10 +1993,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>2038</v>
+        <v>2060</v>
       </c>
       <c r="C28" s="2">
-        <v>17506</v>
+        <v>17503</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1996,10 +2004,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1087</v>
+        <v>1100</v>
       </c>
       <c r="C29" s="2">
-        <v>15455</v>
+        <v>15447</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2018,10 +2026,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C31" s="2">
-        <v>3405</v>
+        <v>3404</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2029,10 +2037,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="C32" s="2">
-        <v>4019</v>
+        <v>4024</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -2040,10 +2048,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="C33" s="2">
-        <v>6116</v>
+        <v>6097</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2051,10 +2059,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C34" s="2">
-        <v>3514</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2073,10 +2081,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>12857</v>
+        <v>13013</v>
       </c>
       <c r="C36" s="2">
-        <v>152403</v>
+        <v>152405</v>
       </c>
     </row>
   </sheetData>
@@ -2155,10 +2163,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C7" s="2">
-        <v>2583</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2177,7 +2185,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C9" s="2">
         <v>1194</v>
@@ -2188,10 +2196,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2210,10 +2218,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C12" s="2">
-        <v>1903</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -2221,10 +2229,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2">
-        <v>3752</v>
+        <v>3795</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2232,10 +2240,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C14" s="2">
-        <v>2721</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2254,10 +2262,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C16" s="2">
-        <v>1851</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2287,10 +2295,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="C19" s="2">
-        <v>1810</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2298,10 +2306,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C20" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2309,10 +2317,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>829</v>
+        <v>846</v>
       </c>
       <c r="C21" s="2">
-        <v>7937</v>
+        <v>7939</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2320,10 +2328,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="C22" s="2">
-        <v>3571</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2331,10 +2339,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C23" s="2">
-        <v>16534</v>
+        <v>16541</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2342,10 +2350,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1637</v>
+        <v>1658</v>
       </c>
       <c r="C24" s="2">
-        <v>16039</v>
+        <v>20676</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2353,10 +2361,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2">
-        <v>2707</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -2364,10 +2372,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C26" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -2375,10 +2383,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C27" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -2386,10 +2394,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1446</v>
+        <v>1471</v>
       </c>
       <c r="C28" s="2">
-        <v>12454</v>
+        <v>12446</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2397,10 +2405,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>903</v>
+        <v>915</v>
       </c>
       <c r="C29" s="2">
-        <v>10946</v>
+        <v>10941</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2419,10 +2427,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C31" s="2">
-        <v>1843</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2430,10 +2438,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C32" s="2">
-        <v>2226</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -2441,10 +2449,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C33" s="2">
-        <v>2946</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2452,10 +2460,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C34" s="2">
-        <v>2534</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2474,10 +2482,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>9582</v>
+        <v>9732</v>
       </c>
       <c r="C36" s="2">
-        <v>99571</v>
+        <v>104300</v>
       </c>
     </row>
   </sheetData>
@@ -2511,10 +2519,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -2556,10 +2564,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C7" s="2">
-        <v>1822</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2578,10 +2586,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C9" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2611,10 +2619,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C12" s="2">
-        <v>1695</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -2622,10 +2630,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2">
-        <v>2741</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2633,10 +2641,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C14" s="2">
-        <v>2289</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2655,10 +2663,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C16" s="2">
-        <v>1805</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2688,10 +2696,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="C19" s="2">
-        <v>1474</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2699,10 +2707,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C20" s="2">
-        <v>723</v>
+        <v>735</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2710,10 +2718,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="C21" s="2">
-        <v>6604</v>
+        <v>6624</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2721,10 +2729,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="C22" s="2">
-        <v>2859</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2732,10 +2740,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="C23" s="2">
-        <v>16144</v>
+        <v>16187</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2743,10 +2751,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1404</v>
+        <v>1434</v>
       </c>
       <c r="C24" s="2">
-        <v>13908</v>
+        <v>18593</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2754,7 +2762,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C25" s="2">
         <v>2354</v>
@@ -2765,10 +2773,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C26" s="2">
-        <v>604</v>
+        <v>610</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -2776,10 +2784,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C27" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -2787,10 +2795,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1206</v>
+        <v>1221</v>
       </c>
       <c r="C28" s="2">
-        <v>10125</v>
+        <v>10146</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2798,10 +2806,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>811</v>
+        <v>855</v>
       </c>
       <c r="C29" s="2">
-        <v>9589</v>
+        <v>9757</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2820,10 +2828,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C31" s="2">
-        <v>1463</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2831,10 +2839,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="C32" s="2">
-        <v>1583</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -2842,10 +2850,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="C33" s="2">
-        <v>2166</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2853,10 +2861,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="C34" s="2">
-        <v>2028</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2875,10 +2883,812 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>8014</v>
+        <v>8214</v>
       </c>
       <c r="C36" s="2">
-        <v>84842</v>
+        <v>90003</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="58.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>77</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>23</v>
+      </c>
+      <c r="C8" s="2">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>95</v>
+      </c>
+      <c r="C9" s="2">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>17</v>
+      </c>
+      <c r="C11" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>97</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>116</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>99</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>58</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2">
+        <v>247</v>
+      </c>
+      <c r="C19" s="2">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2">
+        <v>128</v>
+      </c>
+      <c r="C20" s="2">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2">
+        <v>462</v>
+      </c>
+      <c r="C21" s="2">
+        <v>3918</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2">
+        <v>332</v>
+      </c>
+      <c r="C22" s="2">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2">
+        <v>273</v>
+      </c>
+      <c r="C23" s="2">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1028</v>
+      </c>
+      <c r="C24" s="2">
+        <v>14702</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2">
+        <v>140</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2">
+        <v>80</v>
+      </c>
+      <c r="C26" s="2">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2">
+        <v>37</v>
+      </c>
+      <c r="C27" s="2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2">
+        <v>786</v>
+      </c>
+      <c r="C28" s="2">
+        <v>6711</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2">
+        <v>620</v>
+      </c>
+      <c r="C29" s="2">
+        <v>7679</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2">
+        <v>73</v>
+      </c>
+      <c r="C31" s="2">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="2">
+        <v>161</v>
+      </c>
+      <c r="C32" s="2">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2">
+        <v>195</v>
+      </c>
+      <c r="C33" s="2">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="2">
+        <v>250</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="2">
+        <v>5435</v>
+      </c>
+      <c r="C36" s="2">
+        <v>67330</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="58.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>63</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>26</v>
+      </c>
+      <c r="C8" s="2">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>96</v>
+      </c>
+      <c r="C9" s="2">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>11</v>
+      </c>
+      <c r="C10" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>89</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>100</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>86</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>54</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2">
+        <v>275</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2">
+        <v>107</v>
+      </c>
+      <c r="C20" s="2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2">
+        <v>451</v>
+      </c>
+      <c r="C21" s="2">
+        <v>3595</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2">
+        <v>284</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2">
+        <v>262</v>
+      </c>
+      <c r="C23" s="2">
+        <v>14472</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1086</v>
+      </c>
+      <c r="C24" s="2">
+        <v>15206</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2">
+        <v>127</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2">
+        <v>78</v>
+      </c>
+      <c r="C26" s="2">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2">
+        <v>41</v>
+      </c>
+      <c r="C27" s="2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2">
+        <v>715</v>
+      </c>
+      <c r="C28" s="2">
+        <v>5684</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2">
+        <v>566</v>
+      </c>
+      <c r="C29" s="2">
+        <v>7125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2">
+        <v>115</v>
+      </c>
+      <c r="C31" s="2">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="2">
+        <v>155</v>
+      </c>
+      <c r="C32" s="2">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2">
+        <v>199</v>
+      </c>
+      <c r="C33" s="2">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="2">
+        <v>270</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="2">
+        <v>5296</v>
+      </c>
+      <c r="C36" s="2">
+        <v>63185</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Ausz KonPe KTZH.xlsx
+++ b/KAE Ausz KonPe KTZH.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Werkstatt\Amtsleitung\Monitoring Covid19\Produktion\Versand\Externe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\STAT\01_Post\Schlaepfer\covid19monitoring\economy_AWA_private\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" firstSheet="1" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895"/>
   </bookViews>
   <sheets>
     <sheet name="März 2020" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <sheet name="Juli 2020" sheetId="5" r:id="rId5"/>
     <sheet name="August 2020" sheetId="6" r:id="rId6"/>
     <sheet name="September 2020" sheetId="7" r:id="rId7"/>
-    <sheet name="Oktober 2020" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -31,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="46">
   <si>
     <t>Metriken</t>
   </si>
@@ -169,15 +168,12 @@
   </si>
   <si>
     <t>August 2020</t>
-  </si>
-  <si>
-    <t>Oktober 2020</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -237,7 +233,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3293,405 +3289,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="58.5703125" customWidth="1"/>
-    <col min="2" max="2" width="39.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.42578125" style="2" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2">
-        <v>63</v>
-      </c>
-      <c r="C7" s="2">
-        <v>1275</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2">
-        <v>26</v>
-      </c>
-      <c r="C8" s="2">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2">
-        <v>96</v>
-      </c>
-      <c r="C9" s="2">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2">
-        <v>11</v>
-      </c>
-      <c r="C10" s="2">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2">
-        <v>89</v>
-      </c>
-      <c r="C12" s="2">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2">
-        <v>100</v>
-      </c>
-      <c r="C13" s="2">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2">
-        <v>86</v>
-      </c>
-      <c r="C14" s="2">
-        <v>1752</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2">
-        <v>54</v>
-      </c>
-      <c r="C16" s="2">
-        <v>1439</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="2">
-        <v>275</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="2">
-        <v>107</v>
-      </c>
-      <c r="C20" s="2">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="2">
-        <v>451</v>
-      </c>
-      <c r="C21" s="2">
-        <v>3595</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="2">
-        <v>284</v>
-      </c>
-      <c r="C22" s="2">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" s="2">
-        <v>262</v>
-      </c>
-      <c r="C23" s="2">
-        <v>14472</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="2">
-        <v>1086</v>
-      </c>
-      <c r="C24" s="2">
-        <v>15206</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="2">
-        <v>127</v>
-      </c>
-      <c r="C25" s="2">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="2">
-        <v>78</v>
-      </c>
-      <c r="C26" s="2">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="2">
-        <v>41</v>
-      </c>
-      <c r="C27" s="2">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="2">
-        <v>715</v>
-      </c>
-      <c r="C28" s="2">
-        <v>5684</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="2">
-        <v>566</v>
-      </c>
-      <c r="C29" s="2">
-        <v>7125</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" s="2">
-        <v>115</v>
-      </c>
-      <c r="C31" s="2">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="2">
-        <v>155</v>
-      </c>
-      <c r="C32" s="2">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="2">
-        <v>199</v>
-      </c>
-      <c r="C33" s="2">
-        <v>1381</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="2">
-        <v>270</v>
-      </c>
-      <c r="C34" s="2">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B36" s="2">
-        <v>5296</v>
-      </c>
-      <c r="C36" s="2">
-        <v>63185</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/KAE Ausz KonPe KTZH.xlsx
+++ b/KAE Ausz KonPe KTZH.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="März 2020" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Juli 2020" sheetId="5" r:id="rId5"/>
     <sheet name="August 2020" sheetId="6" r:id="rId6"/>
     <sheet name="September 2020" sheetId="7" r:id="rId7"/>
+    <sheet name="Oktober 2020" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="47">
   <si>
     <t>Metriken</t>
   </si>
@@ -168,6 +169,9 @@
   </si>
   <si>
     <t>August 2020</t>
+  </si>
+  <si>
+    <t>Oktober 2020</t>
   </si>
 </sst>
 </file>
@@ -623,7 +627,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C13" s="2">
         <v>486</v>
@@ -689,10 +693,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C19" s="2">
-        <v>3592</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -700,10 +704,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C20" s="2">
-        <v>3537</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -711,10 +715,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1330</v>
+        <v>1336</v>
       </c>
       <c r="C21" s="2">
-        <v>10027</v>
+        <v>10025</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -722,10 +726,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1925</v>
+        <v>1930</v>
       </c>
       <c r="C22" s="2">
-        <v>12235</v>
+        <v>12158</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -733,7 +737,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C23" s="2">
         <v>16050</v>
@@ -744,10 +748,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3192</v>
+        <v>3240</v>
       </c>
       <c r="C24" s="2">
-        <v>34202</v>
+        <v>34218</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -755,7 +759,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C25" s="2">
         <v>2414</v>
@@ -766,10 +770,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C26" s="2">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -777,10 +781,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C27" s="2">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -788,10 +792,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>2505</v>
+        <v>2515</v>
       </c>
       <c r="C28" s="2">
-        <v>20973</v>
+        <v>21007</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -799,7 +803,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1289</v>
+        <v>1295</v>
       </c>
       <c r="C29" s="2">
         <v>23542</v>
@@ -821,10 +825,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="C31" s="2">
-        <v>6500</v>
+        <v>6501</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -832,10 +836,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>2202</v>
+        <v>2211</v>
       </c>
       <c r="C32" s="2">
-        <v>12359</v>
+        <v>12355</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -843,7 +847,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="C33" s="2">
         <v>9907</v>
@@ -854,10 +858,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>1594</v>
+        <v>1604</v>
       </c>
       <c r="C34" s="2">
-        <v>6650</v>
+        <v>6654</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -876,10 +880,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>19850</v>
+        <v>19969</v>
       </c>
       <c r="C36" s="2">
-        <v>176784</v>
+        <v>176781</v>
       </c>
     </row>
   </sheetData>
@@ -978,7 +982,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C9" s="2">
         <v>1966</v>
@@ -1011,10 +1015,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C12" s="2">
-        <v>2352</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1022,10 +1026,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C13" s="2">
-        <v>5497</v>
+        <v>5499</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1088,10 +1092,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>1378</v>
+        <v>1383</v>
       </c>
       <c r="C19" s="2">
-        <v>7019</v>
+        <v>7017</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1099,10 +1103,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C20" s="2">
-        <v>5850</v>
+        <v>5879</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1110,10 +1114,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>2000</v>
+        <v>2008</v>
       </c>
       <c r="C21" s="2">
-        <v>19346</v>
+        <v>19340</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1121,10 +1125,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>2127</v>
+        <v>2134</v>
       </c>
       <c r="C22" s="2">
-        <v>14377</v>
+        <v>14307</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1132,7 +1136,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="C23" s="2">
         <v>20191</v>
@@ -1143,10 +1147,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3168</v>
+        <v>3223</v>
       </c>
       <c r="C24" s="2">
-        <v>36146</v>
+        <v>36178</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1154,10 +1158,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C25" s="2">
-        <v>5560</v>
+        <v>5558</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1165,7 +1169,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C26" s="2">
         <v>1723</v>
@@ -1176,7 +1180,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C27" s="2">
         <v>1297</v>
@@ -1187,10 +1191,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>3728</v>
+        <v>3739</v>
       </c>
       <c r="C28" s="2">
-        <v>33026</v>
+        <v>33038</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1198,10 +1202,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1775</v>
+        <v>1784</v>
       </c>
       <c r="C29" s="2">
-        <v>31695</v>
+        <v>31700</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1220,10 +1224,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="C31" s="2">
-        <v>8116</v>
+        <v>8119</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1231,10 +1235,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>2898</v>
+        <v>2907</v>
       </c>
       <c r="C32" s="2">
-        <v>22026</v>
+        <v>22009</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1242,7 +1246,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C33" s="2">
         <v>11949</v>
@@ -1253,10 +1257,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>1701</v>
+        <v>1711</v>
       </c>
       <c r="C34" s="2">
-        <v>8389</v>
+        <v>8392</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1275,10 +1279,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>25489</v>
+        <v>25632</v>
       </c>
       <c r="C36" s="2">
-        <v>253836</v>
+        <v>253826</v>
       </c>
     </row>
   </sheetData>
@@ -1357,10 +1361,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C7" s="2">
-        <v>5326</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1379,7 +1383,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C9" s="2">
         <v>1985</v>
@@ -1423,7 +1427,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C13" s="2">
         <v>6548</v>
@@ -1489,7 +1493,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="C19" s="2">
         <v>5682</v>
@@ -1500,10 +1504,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C20" s="2">
-        <v>4060</v>
+        <v>4083</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1511,10 +1515,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1799</v>
+        <v>1807</v>
       </c>
       <c r="C21" s="2">
-        <v>17738</v>
+        <v>17737</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1522,10 +1526,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1766</v>
+        <v>1773</v>
       </c>
       <c r="C22" s="2">
-        <v>11930</v>
+        <v>11876</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1533,7 +1537,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C23" s="2">
         <v>19456</v>
@@ -1544,10 +1548,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2926</v>
+        <v>2979</v>
       </c>
       <c r="C24" s="2">
-        <v>34406</v>
+        <v>34460</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1555,7 +1559,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C25" s="2">
         <v>5572</v>
@@ -1566,7 +1570,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C26" s="2">
         <v>1665</v>
@@ -1577,7 +1581,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C27" s="2">
         <v>1228</v>
@@ -1588,10 +1592,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>3578</v>
+        <v>3597</v>
       </c>
       <c r="C28" s="2">
-        <v>29317</v>
+        <v>29343</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1599,10 +1603,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1618</v>
+        <v>1626</v>
       </c>
       <c r="C29" s="2">
-        <v>21130</v>
+        <v>21133</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1621,10 +1625,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="C31" s="2">
-        <v>6868</v>
+        <v>6871</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1632,10 +1636,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>1528</v>
+        <v>1536</v>
       </c>
       <c r="C32" s="2">
-        <v>10078</v>
+        <v>10075</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1643,10 +1647,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="C33" s="2">
-        <v>11440</v>
+        <v>11442</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1654,10 +1658,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>943</v>
+        <v>957</v>
       </c>
       <c r="C34" s="2">
-        <v>5695</v>
+        <v>5701</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1676,10 +1680,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>21515</v>
+        <v>21664</v>
       </c>
       <c r="C36" s="2">
-        <v>214970</v>
+        <v>215033</v>
       </c>
     </row>
   </sheetData>
@@ -1758,10 +1762,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C7" s="2">
-        <v>3673</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1769,7 +1773,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C8" s="2">
         <v>485</v>
@@ -1780,10 +1784,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C9" s="2">
-        <v>1565</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1791,10 +1795,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1813,10 +1817,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C12" s="2">
-        <v>2457</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1824,7 +1828,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C13" s="2">
         <v>5576</v>
@@ -1857,10 +1861,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C16" s="2">
-        <v>2259</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1890,10 +1894,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="C19" s="2">
-        <v>2741</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1901,10 +1905,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C20" s="2">
-        <v>1493</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1912,10 +1916,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1136</v>
+        <v>1146</v>
       </c>
       <c r="C21" s="2">
-        <v>11148</v>
+        <v>11141</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1923,10 +1927,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="C22" s="2">
-        <v>5558</v>
+        <v>5517</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1934,10 +1938,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C23" s="2">
-        <v>29699</v>
+        <v>29692</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1945,10 +1949,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2114</v>
+        <v>2166</v>
       </c>
       <c r="C24" s="2">
-        <v>25341</v>
+        <v>25345</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1956,10 +1960,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C25" s="2">
-        <v>3774</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1967,10 +1971,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2">
-        <v>903</v>
+        <v>897</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -1978,10 +1982,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C27" s="2">
-        <v>779</v>
+        <v>773</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -1989,10 +1993,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>2060</v>
+        <v>2084</v>
       </c>
       <c r="C28" s="2">
-        <v>17503</v>
+        <v>17475</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2000,10 +2004,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1100</v>
+        <v>1113</v>
       </c>
       <c r="C29" s="2">
-        <v>15447</v>
+        <v>15434</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2022,10 +2026,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C31" s="2">
-        <v>3404</v>
+        <v>3406</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2033,10 +2037,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="C32" s="2">
-        <v>4024</v>
+        <v>4007</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -2044,10 +2048,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C33" s="2">
-        <v>6097</v>
+        <v>6098</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2055,10 +2059,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>641</v>
+        <v>655</v>
       </c>
       <c r="C34" s="2">
-        <v>3510</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2077,10 +2081,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>13013</v>
+        <v>13186</v>
       </c>
       <c r="C36" s="2">
-        <v>152405</v>
+        <v>152268</v>
       </c>
     </row>
   </sheetData>
@@ -2159,10 +2163,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C7" s="2">
-        <v>2616</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2170,7 +2174,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" s="2">
         <v>356</v>
@@ -2181,10 +2185,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C9" s="2">
-        <v>1194</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2192,10 +2196,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -2214,10 +2218,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C12" s="2">
-        <v>1908</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -2225,7 +2229,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C13" s="2">
         <v>3795</v>
@@ -2258,10 +2262,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C16" s="2">
-        <v>1850</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2291,7 +2295,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C19" s="2">
         <v>1824</v>
@@ -2302,10 +2306,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C20" s="2">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2313,10 +2317,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>846</v>
+        <v>855</v>
       </c>
       <c r="C21" s="2">
-        <v>7939</v>
+        <v>7931</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2324,10 +2328,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C22" s="2">
-        <v>3566</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2335,10 +2339,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C23" s="2">
-        <v>16541</v>
+        <v>16529</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2346,10 +2350,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1658</v>
+        <v>1700</v>
       </c>
       <c r="C24" s="2">
-        <v>20676</v>
+        <v>20677</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2357,10 +2361,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C25" s="2">
-        <v>2705</v>
+        <v>2704</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -2368,10 +2372,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C26" s="2">
-        <v>644</v>
+        <v>638</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -2379,10 +2383,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C27" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -2390,10 +2394,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1471</v>
+        <v>1493</v>
       </c>
       <c r="C28" s="2">
-        <v>12446</v>
+        <v>12450</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2401,7 +2405,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>915</v>
+        <v>930</v>
       </c>
       <c r="C29" s="2">
         <v>10941</v>
@@ -2423,10 +2427,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C31" s="2">
-        <v>1846</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2434,10 +2438,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C32" s="2">
-        <v>2222</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -2445,10 +2449,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C33" s="2">
-        <v>2948</v>
+        <v>2949</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2456,10 +2460,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="C34" s="2">
-        <v>2533</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2478,10 +2482,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>9732</v>
+        <v>9881</v>
       </c>
       <c r="C36" s="2">
-        <v>104300</v>
+        <v>104258</v>
       </c>
     </row>
   </sheetData>
@@ -2560,10 +2564,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" s="2">
-        <v>1845</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2582,10 +2586,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C9" s="2">
-        <v>757</v>
+        <v>752</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2615,10 +2619,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C12" s="2">
-        <v>1702</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -2626,7 +2630,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2">
         <v>2742</v>
@@ -2659,7 +2663,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C16" s="2">
         <v>1804</v>
@@ -2692,10 +2696,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="C19" s="2">
-        <v>1510</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2703,10 +2707,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C20" s="2">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2714,10 +2718,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="C21" s="2">
-        <v>6624</v>
+        <v>6618</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2725,10 +2729,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="C22" s="2">
-        <v>2854</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2736,10 +2740,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="C23" s="2">
-        <v>16187</v>
+        <v>16198</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2747,10 +2751,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1434</v>
+        <v>1478</v>
       </c>
       <c r="C24" s="2">
-        <v>18593</v>
+        <v>18579</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2758,7 +2762,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C25" s="2">
         <v>2354</v>
@@ -2769,10 +2773,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C26" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -2780,10 +2784,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C27" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -2791,10 +2795,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1221</v>
+        <v>1251</v>
       </c>
       <c r="C28" s="2">
-        <v>10146</v>
+        <v>10112</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2802,10 +2806,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>855</v>
+        <v>864</v>
       </c>
       <c r="C29" s="2">
-        <v>9757</v>
+        <v>9749</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2824,10 +2828,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C31" s="2">
-        <v>1503</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2835,10 +2839,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C32" s="2">
-        <v>1602</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -2846,10 +2850,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C33" s="2">
-        <v>2196</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2857,10 +2861,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="C34" s="2">
-        <v>2047</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2879,10 +2883,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>8214</v>
+        <v>8373</v>
       </c>
       <c r="C36" s="2">
-        <v>90003</v>
+        <v>89979</v>
       </c>
     </row>
   </sheetData>
@@ -2961,10 +2965,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C7" s="2">
-        <v>1514</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2983,10 +2987,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C9" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -3016,10 +3020,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C12" s="2">
-        <v>1092</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -3027,7 +3031,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C13" s="2">
         <v>1574</v>
@@ -3093,10 +3097,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C19" s="2">
-        <v>923</v>
+        <v>939</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -3104,10 +3108,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C20" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -3115,10 +3119,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="C21" s="2">
-        <v>3918</v>
+        <v>3955</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3126,10 +3130,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="C22" s="2">
-        <v>2051</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3137,10 +3141,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="C23" s="2">
-        <v>14500</v>
+        <v>14503</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -3148,10 +3152,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1028</v>
+        <v>1074</v>
       </c>
       <c r="C24" s="2">
-        <v>14702</v>
+        <v>14768</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -3159,10 +3163,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C25" s="2">
-        <v>1628</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -3170,10 +3174,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C26" s="2">
-        <v>429</v>
+        <v>438</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -3181,10 +3185,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C27" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -3192,10 +3196,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>786</v>
+        <v>823</v>
       </c>
       <c r="C28" s="2">
-        <v>6711</v>
+        <v>6779</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -3203,10 +3207,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>620</v>
+        <v>638</v>
       </c>
       <c r="C29" s="2">
-        <v>7679</v>
+        <v>7740</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -3225,10 +3229,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C31" s="2">
-        <v>751</v>
+        <v>761</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -3236,10 +3240,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C32" s="2">
-        <v>755</v>
+        <v>762</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -3247,10 +3251,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C33" s="2">
-        <v>1377</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -3258,10 +3262,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C34" s="2">
-        <v>1275</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -3280,10 +3284,411 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>5435</v>
+        <v>5623</v>
       </c>
       <c r="C36" s="2">
-        <v>67330</v>
+        <v>67851</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="58.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>72</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>27</v>
+      </c>
+      <c r="C8" s="2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>101</v>
+      </c>
+      <c r="C9" s="2">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>12</v>
+      </c>
+      <c r="C10" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>96</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>105</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>87</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>59</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2">
+        <v>295</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2">
+        <v>115</v>
+      </c>
+      <c r="C20" s="2">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2">
+        <v>475</v>
+      </c>
+      <c r="C21" s="2">
+        <v>3889</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2">
+        <v>324</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2">
+        <v>286</v>
+      </c>
+      <c r="C23" s="2">
+        <v>14558</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1195</v>
+      </c>
+      <c r="C24" s="2">
+        <v>15817</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2">
+        <v>133</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2">
+        <v>90</v>
+      </c>
+      <c r="C26" s="2">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2">
+        <v>42</v>
+      </c>
+      <c r="C27" s="2">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2">
+        <v>766</v>
+      </c>
+      <c r="C28" s="2">
+        <v>6129</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2">
+        <v>602</v>
+      </c>
+      <c r="C29" s="2">
+        <v>7652</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2">
+        <v>123</v>
+      </c>
+      <c r="C31" s="2">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="2">
+        <v>165</v>
+      </c>
+      <c r="C32" s="2">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2">
+        <v>205</v>
+      </c>
+      <c r="C33" s="2">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="2">
+        <v>292</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="2">
+        <v>5710</v>
+      </c>
+      <c r="C36" s="2">
+        <v>66664</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Ausz KonPe KTZH.xlsx
+++ b/KAE Ausz KonPe KTZH.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="März 2020" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="August 2020" sheetId="6" r:id="rId6"/>
     <sheet name="September 2020" sheetId="7" r:id="rId7"/>
     <sheet name="Oktober 2020" sheetId="8" r:id="rId8"/>
+    <sheet name="November 2020" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="48">
   <si>
     <t>Metriken</t>
   </si>
@@ -172,6 +173,9 @@
   </si>
   <si>
     <t>Oktober 2020</t>
+  </si>
+  <si>
+    <t>November 2020</t>
   </si>
 </sst>
 </file>
@@ -561,7 +565,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C7" s="2">
         <v>4461</v>
@@ -583,7 +587,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C9" s="2">
         <v>901</v>
@@ -638,10 +642,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C14" s="2">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -660,10 +664,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C16" s="2">
-        <v>1832</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -693,7 +697,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="C19" s="2">
         <v>3591</v>
@@ -704,10 +708,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="C20" s="2">
-        <v>3566</v>
+        <v>3565</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -715,10 +719,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1336</v>
+        <v>1341</v>
       </c>
       <c r="C21" s="2">
-        <v>10025</v>
+        <v>10028</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -726,7 +730,7 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1930</v>
+        <v>1939</v>
       </c>
       <c r="C22" s="2">
         <v>12158</v>
@@ -737,10 +741,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C23" s="2">
-        <v>16050</v>
+        <v>16047</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -748,10 +752,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3240</v>
+        <v>3273</v>
       </c>
       <c r="C24" s="2">
-        <v>34218</v>
+        <v>34222</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -770,7 +774,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C26" s="2">
         <v>1247</v>
@@ -781,7 +785,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C27" s="2">
         <v>897</v>
@@ -792,10 +796,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>2515</v>
+        <v>2524</v>
       </c>
       <c r="C28" s="2">
-        <v>21007</v>
+        <v>20995</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -803,10 +807,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1295</v>
+        <v>1302</v>
       </c>
       <c r="C29" s="2">
-        <v>23542</v>
+        <v>23541</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -825,7 +829,7 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="C31" s="2">
         <v>6501</v>
@@ -836,10 +840,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>2211</v>
+        <v>2215</v>
       </c>
       <c r="C32" s="2">
-        <v>12355</v>
+        <v>12436</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -858,10 +862,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="C34" s="2">
-        <v>6654</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -880,10 +884,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>19969</v>
+        <v>20061</v>
       </c>
       <c r="C36" s="2">
-        <v>176781</v>
+        <v>176847</v>
       </c>
     </row>
   </sheetData>
@@ -960,7 +964,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C7" s="2">
         <v>5761</v>
@@ -982,10 +986,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C9" s="2">
-        <v>1966</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1015,7 +1019,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C12" s="2">
         <v>2353</v>
@@ -1026,7 +1030,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C13" s="2">
         <v>5499</v>
@@ -1037,10 +1041,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C14" s="2">
-        <v>2951</v>
+        <v>2949</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1059,10 +1063,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C16" s="2">
-        <v>2999</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1092,7 +1096,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>1383</v>
+        <v>1389</v>
       </c>
       <c r="C19" s="2">
         <v>7017</v>
@@ -1103,10 +1107,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="C20" s="2">
-        <v>5879</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1114,10 +1118,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>2008</v>
+        <v>2015</v>
       </c>
       <c r="C21" s="2">
-        <v>19340</v>
+        <v>19341</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1125,7 +1129,7 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>2134</v>
+        <v>2143</v>
       </c>
       <c r="C22" s="2">
         <v>14307</v>
@@ -1136,10 +1140,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C23" s="2">
-        <v>20191</v>
+        <v>20190</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1147,10 +1151,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3223</v>
+        <v>3255</v>
       </c>
       <c r="C24" s="2">
-        <v>36178</v>
+        <v>36185</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1158,7 +1162,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C25" s="2">
         <v>5558</v>
@@ -1169,7 +1173,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C26" s="2">
         <v>1723</v>
@@ -1191,10 +1195,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>3739</v>
+        <v>3753</v>
       </c>
       <c r="C28" s="2">
-        <v>33038</v>
+        <v>33034</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1202,10 +1206,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1784</v>
+        <v>1790</v>
       </c>
       <c r="C29" s="2">
-        <v>31700</v>
+        <v>31698</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1224,7 +1228,7 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="C31" s="2">
         <v>8119</v>
@@ -1235,10 +1239,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>2907</v>
+        <v>2911</v>
       </c>
       <c r="C32" s="2">
-        <v>22009</v>
+        <v>22004</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1246,10 +1250,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C33" s="2">
-        <v>11949</v>
+        <v>11952</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1257,7 +1261,7 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>1711</v>
+        <v>1714</v>
       </c>
       <c r="C34" s="2">
         <v>8392</v>
@@ -1279,10 +1283,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>25632</v>
+        <v>25734</v>
       </c>
       <c r="C36" s="2">
-        <v>253826</v>
+        <v>253817</v>
       </c>
     </row>
   </sheetData>
@@ -1361,7 +1365,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C7" s="2">
         <v>5330</v>
@@ -1383,10 +1387,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C9" s="2">
-        <v>1985</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1416,7 +1420,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C12" s="2">
         <v>2987</v>
@@ -1427,7 +1431,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C13" s="2">
         <v>6548</v>
@@ -1438,10 +1442,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C14" s="2">
-        <v>3516</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1460,10 +1464,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C16" s="2">
-        <v>3218</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1493,7 +1497,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="C19" s="2">
         <v>5682</v>
@@ -1504,10 +1508,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="C20" s="2">
-        <v>4083</v>
+        <v>4081</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1515,7 +1519,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1807</v>
+        <v>1814</v>
       </c>
       <c r="C21" s="2">
         <v>17737</v>
@@ -1526,10 +1530,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1773</v>
+        <v>1785</v>
       </c>
       <c r="C22" s="2">
-        <v>11876</v>
+        <v>11877</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1537,10 +1541,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C23" s="2">
-        <v>19456</v>
+        <v>19455</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1548,10 +1552,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2979</v>
+        <v>3011</v>
       </c>
       <c r="C24" s="2">
-        <v>34460</v>
+        <v>34465</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1559,10 +1563,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="C25" s="2">
-        <v>5572</v>
+        <v>5569</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1592,10 +1596,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>3597</v>
+        <v>3613</v>
       </c>
       <c r="C28" s="2">
-        <v>29343</v>
+        <v>29353</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1603,10 +1607,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1626</v>
+        <v>1632</v>
       </c>
       <c r="C29" s="2">
-        <v>21133</v>
+        <v>21131</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1625,10 +1629,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="C31" s="2">
-        <v>6871</v>
+        <v>6872</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1636,10 +1640,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>1536</v>
+        <v>1540</v>
       </c>
       <c r="C32" s="2">
-        <v>10075</v>
+        <v>10071</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1647,7 +1651,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C33" s="2">
         <v>11442</v>
@@ -1658,10 +1662,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="C34" s="2">
-        <v>5701</v>
+        <v>5693</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1680,10 +1684,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>21664</v>
+        <v>21772</v>
       </c>
       <c r="C36" s="2">
-        <v>215033</v>
+        <v>215008</v>
       </c>
     </row>
   </sheetData>
@@ -1762,10 +1766,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C7" s="2">
-        <v>3680</v>
+        <v>3679</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1784,10 +1788,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C9" s="2">
-        <v>1561</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1817,10 +1821,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C12" s="2">
-        <v>2455</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1828,10 +1832,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C13" s="2">
-        <v>5576</v>
+        <v>5756</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1839,10 +1843,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C14" s="2">
-        <v>2893</v>
+        <v>2891</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1861,10 +1865,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2">
-        <v>2258</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1894,10 +1898,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>753</v>
+        <v>766</v>
       </c>
       <c r="C19" s="2">
-        <v>2738</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1905,10 +1909,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="C20" s="2">
-        <v>1490</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1916,10 +1920,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1146</v>
+        <v>1154</v>
       </c>
       <c r="C21" s="2">
-        <v>11141</v>
+        <v>11136</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1927,10 +1931,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>795</v>
+        <v>807</v>
       </c>
       <c r="C22" s="2">
-        <v>5517</v>
+        <v>5515</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1938,10 +1942,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="C23" s="2">
-        <v>29692</v>
+        <v>29686</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1949,10 +1953,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2166</v>
+        <v>2204</v>
       </c>
       <c r="C24" s="2">
-        <v>25345</v>
+        <v>25332</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1960,10 +1964,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C25" s="2">
-        <v>3772</v>
+        <v>3766</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1971,10 +1975,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2">
-        <v>897</v>
+        <v>893</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -1993,10 +1997,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>2084</v>
+        <v>2097</v>
       </c>
       <c r="C28" s="2">
-        <v>17475</v>
+        <v>17432</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2004,10 +2008,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1113</v>
+        <v>1129</v>
       </c>
       <c r="C29" s="2">
-        <v>15434</v>
+        <v>15466</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2026,10 +2030,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C31" s="2">
-        <v>3406</v>
+        <v>3403</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2037,10 +2041,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="C32" s="2">
-        <v>4007</v>
+        <v>4005</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -2048,10 +2052,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C33" s="2">
-        <v>6098</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2059,10 +2063,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="C34" s="2">
-        <v>3500</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2081,10 +2085,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>13186</v>
+        <v>13343</v>
       </c>
       <c r="C36" s="2">
-        <v>152268</v>
+        <v>152356</v>
       </c>
     </row>
   </sheetData>
@@ -2163,10 +2167,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C7" s="2">
-        <v>2655</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2185,10 +2189,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C9" s="2">
-        <v>1190</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2218,7 +2222,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2">
         <v>1907</v>
@@ -2229,10 +2233,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C13" s="2">
-        <v>3795</v>
+        <v>3794</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2240,10 +2244,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C14" s="2">
-        <v>2724</v>
+        <v>2722</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2262,10 +2266,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C16" s="2">
-        <v>1849</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2295,10 +2299,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="C19" s="2">
-        <v>1824</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2306,10 +2310,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C20" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2317,10 +2321,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="C21" s="2">
-        <v>7931</v>
+        <v>7926</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2328,10 +2332,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>588</v>
+        <v>602</v>
       </c>
       <c r="C22" s="2">
-        <v>3524</v>
+        <v>3539</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2339,10 +2343,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C23" s="2">
-        <v>16529</v>
+        <v>16524</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2350,10 +2354,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1700</v>
+        <v>1736</v>
       </c>
       <c r="C24" s="2">
-        <v>20677</v>
+        <v>20675</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2361,10 +2365,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C25" s="2">
-        <v>2704</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -2372,10 +2376,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C26" s="2">
-        <v>638</v>
+        <v>634</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -2394,10 +2398,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1493</v>
+        <v>1502</v>
       </c>
       <c r="C28" s="2">
-        <v>12450</v>
+        <v>12463</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2405,10 +2409,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>930</v>
+        <v>944</v>
       </c>
       <c r="C29" s="2">
-        <v>10941</v>
+        <v>10933</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2427,10 +2431,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C31" s="2">
-        <v>1847</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2438,10 +2442,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C32" s="2">
-        <v>2219</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -2449,10 +2453,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C33" s="2">
-        <v>2949</v>
+        <v>2952</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2460,7 +2464,7 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="C34" s="2">
         <v>2529</v>
@@ -2482,10 +2486,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>9881</v>
+        <v>10021</v>
       </c>
       <c r="C36" s="2">
-        <v>104258</v>
+        <v>104230</v>
       </c>
     </row>
   </sheetData>
@@ -2564,7 +2568,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C7" s="2">
         <v>1849</v>
@@ -2586,10 +2590,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C9" s="2">
-        <v>752</v>
+        <v>887</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2619,10 +2623,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C12" s="2">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -2630,7 +2634,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2">
         <v>2742</v>
@@ -2641,10 +2645,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C14" s="2">
-        <v>2326</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2663,10 +2667,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C16" s="2">
-        <v>1804</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -2696,10 +2700,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="C19" s="2">
-        <v>1512</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2707,10 +2711,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C20" s="2">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2718,10 +2722,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="C21" s="2">
-        <v>6618</v>
+        <v>6613</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2729,10 +2733,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="C22" s="2">
-        <v>2847</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2740,10 +2744,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C23" s="2">
-        <v>16198</v>
+        <v>16195</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2751,10 +2755,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1478</v>
+        <v>1509</v>
       </c>
       <c r="C24" s="2">
-        <v>18579</v>
+        <v>18576</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2762,10 +2766,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C25" s="2">
-        <v>2354</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -2773,10 +2777,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C26" s="2">
-        <v>614</v>
+        <v>610</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -2784,10 +2788,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C27" s="2">
-        <v>492</v>
+        <v>499</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -2795,10 +2799,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1251</v>
+        <v>1259</v>
       </c>
       <c r="C28" s="2">
-        <v>10112</v>
+        <v>10105</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2806,10 +2810,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>864</v>
+        <v>877</v>
       </c>
       <c r="C29" s="2">
-        <v>9749</v>
+        <v>9748</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2828,10 +2832,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C31" s="2">
-        <v>1512</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2839,10 +2843,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C32" s="2">
-        <v>1607</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -2850,10 +2854,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C33" s="2">
-        <v>2209</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2861,10 +2865,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C34" s="2">
-        <v>2046</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2883,10 +2887,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>8373</v>
+        <v>8500</v>
       </c>
       <c r="C36" s="2">
-        <v>89979</v>
+        <v>90090</v>
       </c>
     </row>
   </sheetData>
@@ -2965,7 +2969,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C7" s="2">
         <v>1523</v>
@@ -2987,10 +2991,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -3020,10 +3024,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C12" s="2">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -3031,10 +3035,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2">
-        <v>1574</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -3064,7 +3068,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C16" s="2">
         <v>1559</v>
@@ -3097,10 +3101,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C19" s="2">
-        <v>939</v>
+        <v>942</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -3108,10 +3112,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C20" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -3119,10 +3123,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="C21" s="2">
-        <v>3955</v>
+        <v>3954</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3130,10 +3134,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="C22" s="2">
-        <v>2091</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3141,10 +3145,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="C23" s="2">
-        <v>14503</v>
+        <v>14492</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -3152,10 +3156,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1074</v>
+        <v>1106</v>
       </c>
       <c r="C24" s="2">
-        <v>14768</v>
+        <v>14775</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -3163,7 +3167,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C25" s="2">
         <v>1714</v>
@@ -3174,10 +3178,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C26" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -3185,7 +3189,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C27" s="2">
         <v>196</v>
@@ -3196,10 +3200,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>823</v>
+        <v>842</v>
       </c>
       <c r="C28" s="2">
-        <v>6779</v>
+        <v>7041</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -3207,10 +3211,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>638</v>
+        <v>653</v>
       </c>
       <c r="C29" s="2">
-        <v>7740</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -3228,11 +3232,11 @@
       <c r="A31" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="2">
-        <v>77</v>
-      </c>
-      <c r="C31" s="2">
-        <v>761</v>
+      <c r="B31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -3240,10 +3244,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="C32" s="2">
-        <v>762</v>
+        <v>766</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -3251,10 +3255,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>198</v>
+        <v>137</v>
       </c>
       <c r="C33" s="2">
-        <v>1385</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -3262,10 +3266,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>262</v>
+        <v>509</v>
       </c>
       <c r="C34" s="2">
-        <v>1297</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -3284,10 +3288,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>5623</v>
+        <v>5774</v>
       </c>
       <c r="C36" s="2">
-        <v>67851</v>
+        <v>67956</v>
       </c>
     </row>
   </sheetData>
@@ -3366,10 +3370,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C7" s="2">
-        <v>1341</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -3388,10 +3392,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2">
-        <v>587</v>
+        <v>592</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -3421,10 +3425,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C12" s="2">
-        <v>1340</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -3432,10 +3436,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2">
-        <v>1330</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -3465,7 +3469,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C16" s="2">
         <v>1452</v>
@@ -3498,10 +3502,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="C19" s="2">
-        <v>1086</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -3509,10 +3513,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C20" s="2">
-        <v>332</v>
+        <v>355</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -3520,10 +3524,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="C21" s="2">
-        <v>3889</v>
+        <v>3923</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3531,10 +3535,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="C22" s="2">
-        <v>1817</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3542,10 +3546,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="C23" s="2">
-        <v>14558</v>
+        <v>14580</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -3553,10 +3557,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1195</v>
+        <v>1247</v>
       </c>
       <c r="C24" s="2">
-        <v>15817</v>
+        <v>15973</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -3564,10 +3568,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="C25" s="2">
-        <v>1337</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -3575,10 +3579,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C26" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -3586,10 +3590,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C27" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -3597,10 +3601,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>766</v>
+        <v>805</v>
       </c>
       <c r="C28" s="2">
-        <v>6129</v>
+        <v>6396</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -3608,10 +3612,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>602</v>
+        <v>633</v>
       </c>
       <c r="C29" s="2">
-        <v>7652</v>
+        <v>7835</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -3630,10 +3634,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="C31" s="2">
-        <v>907</v>
+        <v>910</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -3641,10 +3645,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="C32" s="2">
-        <v>733</v>
+        <v>774</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -3652,10 +3656,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>205</v>
+        <v>131</v>
       </c>
       <c r="C33" s="2">
-        <v>1479</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -3663,10 +3667,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>292</v>
+        <v>582</v>
       </c>
       <c r="C34" s="2">
-        <v>1311</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -3685,10 +3689,411 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>5710</v>
+        <v>5994</v>
       </c>
       <c r="C36" s="2">
-        <v>66664</v>
+        <v>68078</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="58.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>121</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>37</v>
+      </c>
+      <c r="C8" s="2">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>103</v>
+      </c>
+      <c r="C9" s="2">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>16</v>
+      </c>
+      <c r="C11" s="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>118</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>96</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>93</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>65</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2">
+        <v>363</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2">
+        <v>153</v>
+      </c>
+      <c r="C20" s="2">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2">
+        <v>561</v>
+      </c>
+      <c r="C21" s="2">
+        <v>4334</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2">
+        <v>466</v>
+      </c>
+      <c r="C22" s="2">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2">
+        <v>319</v>
+      </c>
+      <c r="C23" s="2">
+        <v>14398</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1808</v>
+      </c>
+      <c r="C24" s="2">
+        <v>20780</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2">
+        <v>170</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2">
+        <v>101</v>
+      </c>
+      <c r="C26" s="2">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2">
+        <v>62</v>
+      </c>
+      <c r="C27" s="2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2">
+        <v>989</v>
+      </c>
+      <c r="C28" s="2">
+        <v>8583</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2">
+        <v>683</v>
+      </c>
+      <c r="C29" s="2">
+        <v>8407</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2">
+        <v>80</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="2">
+        <v>107</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2">
+        <v>304</v>
+      </c>
+      <c r="C33" s="2">
+        <v>4374</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="2">
+        <v>730</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="2">
+        <v>7468</v>
+      </c>
+      <c r="C36" s="2">
+        <v>81502</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Ausz KonPe KTZH.xlsx
+++ b/KAE Ausz KonPe KTZH.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" firstSheet="1" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" firstSheet="6" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="März 2020" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="September 2020" sheetId="7" r:id="rId7"/>
     <sheet name="Oktober 2020" sheetId="8" r:id="rId8"/>
     <sheet name="November 2020" sheetId="9" r:id="rId9"/>
+    <sheet name="Dezember 2020" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="49">
   <si>
     <t>Metriken</t>
   </si>
@@ -176,6 +177,9 @@
   </si>
   <si>
     <t>November 2020</t>
+  </si>
+  <si>
+    <t>Dezember 2020</t>
   </si>
 </sst>
 </file>
@@ -587,7 +591,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C9" s="2">
         <v>901</v>
@@ -620,10 +624,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C12" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -697,10 +701,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="C19" s="2">
-        <v>3591</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -708,7 +712,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="C20" s="2">
         <v>3565</v>
@@ -719,10 +723,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1341</v>
+        <v>1347</v>
       </c>
       <c r="C21" s="2">
-        <v>10028</v>
+        <v>10031</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -730,10 +734,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1939</v>
+        <v>1951</v>
       </c>
       <c r="C22" s="2">
-        <v>12158</v>
+        <v>12216</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -741,10 +745,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C23" s="2">
-        <v>16047</v>
+        <v>16048</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -752,10 +756,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3273</v>
+        <v>3314</v>
       </c>
       <c r="C24" s="2">
-        <v>34222</v>
+        <v>34223</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -763,10 +767,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C25" s="2">
-        <v>2414</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -785,10 +789,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C27" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -796,10 +800,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>2524</v>
+        <v>2531</v>
       </c>
       <c r="C28" s="2">
-        <v>20995</v>
+        <v>20954</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -807,10 +811,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="C29" s="2">
-        <v>23541</v>
+        <v>23527</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -840,10 +844,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>2215</v>
+        <v>2218</v>
       </c>
       <c r="C32" s="2">
-        <v>12436</v>
+        <v>12435</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -851,10 +855,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C33" s="2">
-        <v>9907</v>
+        <v>9903</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -862,10 +866,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="C34" s="2">
-        <v>6650</v>
+        <v>6657</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -884,10 +888,411 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>20061</v>
+        <v>20158</v>
       </c>
       <c r="C36" s="2">
-        <v>176847</v>
+        <v>176859</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="58.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>158</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>59</v>
+      </c>
+      <c r="C8" s="2">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>85</v>
+      </c>
+      <c r="C9" s="2">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>94</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>76</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>59</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>51</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2">
+        <v>333</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2">
+        <v>134</v>
+      </c>
+      <c r="C20" s="2">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2">
+        <v>492</v>
+      </c>
+      <c r="C21" s="2">
+        <v>4264</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2">
+        <v>483</v>
+      </c>
+      <c r="C22" s="2">
+        <v>2779</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2">
+        <v>273</v>
+      </c>
+      <c r="C23" s="2">
+        <v>14391</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2">
+        <v>2084</v>
+      </c>
+      <c r="C24" s="2">
+        <v>23644</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2">
+        <v>141</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2">
+        <v>77</v>
+      </c>
+      <c r="C26" s="2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2">
+        <v>63</v>
+      </c>
+      <c r="C27" s="2">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2">
+        <v>875</v>
+      </c>
+      <c r="C28" s="2">
+        <v>7655</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2">
+        <v>632</v>
+      </c>
+      <c r="C29" s="2">
+        <v>8591</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2">
+        <v>182</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="2">
+        <v>195</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2">
+        <v>452</v>
+      </c>
+      <c r="C33" s="2">
+        <v>6929</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="2">
+        <v>349</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="2">
+        <v>7391</v>
+      </c>
+      <c r="C36" s="2">
+        <v>85740</v>
       </c>
     </row>
   </sheetData>
@@ -942,10 +1347,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C5" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -986,7 +1391,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C9" s="2">
         <v>1958</v>
@@ -1019,10 +1424,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C12" s="2">
-        <v>2353</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1030,10 +1435,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C13" s="2">
-        <v>5499</v>
+        <v>5519</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1041,7 +1446,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2">
         <v>2949</v>
@@ -1063,7 +1468,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C16" s="2">
         <v>3001</v>
@@ -1085,7 +1490,7 @@
         <v>33</v>
       </c>
       <c r="B18" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C18" s="2">
         <v>291</v>
@@ -1096,10 +1501,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>1389</v>
+        <v>1399</v>
       </c>
       <c r="C19" s="2">
-        <v>7017</v>
+        <v>7022</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1107,7 +1512,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="C20" s="2">
         <v>5880</v>
@@ -1118,10 +1523,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="C21" s="2">
-        <v>19341</v>
+        <v>19352</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1129,10 +1534,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>2143</v>
+        <v>2158</v>
       </c>
       <c r="C22" s="2">
-        <v>14307</v>
+        <v>14370</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1140,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="C23" s="2">
         <v>20190</v>
@@ -1151,10 +1556,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3255</v>
+        <v>3301</v>
       </c>
       <c r="C24" s="2">
-        <v>36185</v>
+        <v>36222</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1162,10 +1567,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C25" s="2">
-        <v>5558</v>
+        <v>5559</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1184,7 +1589,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C27" s="2">
         <v>1297</v>
@@ -1195,10 +1600,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>3753</v>
+        <v>3759</v>
       </c>
       <c r="C28" s="2">
-        <v>33034</v>
+        <v>32964</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1206,10 +1611,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1790</v>
+        <v>1801</v>
       </c>
       <c r="C29" s="2">
-        <v>31698</v>
+        <v>31763</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1228,7 +1633,7 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="C31" s="2">
         <v>8119</v>
@@ -1239,10 +1644,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>2911</v>
+        <v>2914</v>
       </c>
       <c r="C32" s="2">
-        <v>22004</v>
+        <v>22003</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1250,10 +1655,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>917</v>
+        <v>922</v>
       </c>
       <c r="C33" s="2">
-        <v>11952</v>
+        <v>11911</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1261,10 +1666,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="C34" s="2">
-        <v>8392</v>
+        <v>8391</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1283,10 +1688,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>25734</v>
+        <v>25860</v>
       </c>
       <c r="C36" s="2">
-        <v>253817</v>
+        <v>253903</v>
       </c>
     </row>
   </sheetData>
@@ -1387,7 +1792,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C9" s="2">
         <v>1963</v>
@@ -1431,10 +1836,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C13" s="2">
-        <v>6548</v>
+        <v>6569</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1442,7 +1847,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C14" s="2">
         <v>3514</v>
@@ -1464,7 +1869,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C16" s="2">
         <v>3220</v>
@@ -1486,7 +1891,7 @@
         <v>33</v>
       </c>
       <c r="B18" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C18" s="2">
         <v>231</v>
@@ -1497,10 +1902,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>1200</v>
+        <v>1209</v>
       </c>
       <c r="C19" s="2">
-        <v>5682</v>
+        <v>5683</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1508,10 +1913,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="C20" s="2">
-        <v>4081</v>
+        <v>4086</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1519,10 +1924,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1814</v>
+        <v>1823</v>
       </c>
       <c r="C21" s="2">
-        <v>17737</v>
+        <v>17747</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1530,10 +1935,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1785</v>
+        <v>1798</v>
       </c>
       <c r="C22" s="2">
-        <v>11877</v>
+        <v>11922</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1541,7 +1946,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C23" s="2">
         <v>19455</v>
@@ -1552,10 +1957,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3011</v>
+        <v>3052</v>
       </c>
       <c r="C24" s="2">
-        <v>34465</v>
+        <v>34481</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1563,10 +1968,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C25" s="2">
-        <v>5569</v>
+        <v>5570</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1585,7 +1990,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C27" s="2">
         <v>1228</v>
@@ -1596,10 +2001,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>3613</v>
+        <v>3618</v>
       </c>
       <c r="C28" s="2">
-        <v>29353</v>
+        <v>29298</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1607,10 +2012,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1632</v>
+        <v>1642</v>
       </c>
       <c r="C29" s="2">
-        <v>21131</v>
+        <v>21167</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1629,10 +2034,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C31" s="2">
-        <v>6872</v>
+        <v>6871</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1640,10 +2045,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="C32" s="2">
-        <v>10071</v>
+        <v>10091</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1651,10 +2056,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="C33" s="2">
-        <v>11442</v>
+        <v>11407</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1662,10 +2067,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C34" s="2">
-        <v>5693</v>
+        <v>5692</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1684,10 +2089,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>21772</v>
+        <v>21892</v>
       </c>
       <c r="C36" s="2">
-        <v>215008</v>
+        <v>215071</v>
       </c>
     </row>
   </sheetData>
@@ -1788,10 +2193,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C9" s="2">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1832,10 +2237,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C13" s="2">
-        <v>5756</v>
+        <v>5774</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1843,10 +2248,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C14" s="2">
-        <v>2891</v>
+        <v>2888</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1898,10 +2303,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>766</v>
+        <v>779</v>
       </c>
       <c r="C19" s="2">
-        <v>2727</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1909,10 +2314,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C20" s="2">
-        <v>1486</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1920,10 +2325,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1154</v>
+        <v>1170</v>
       </c>
       <c r="C21" s="2">
-        <v>11136</v>
+        <v>11130</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1931,10 +2336,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>807</v>
+        <v>824</v>
       </c>
       <c r="C22" s="2">
-        <v>5515</v>
+        <v>5529</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1942,7 +2347,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C23" s="2">
         <v>29686</v>
@@ -1953,10 +2358,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2204</v>
+        <v>2245</v>
       </c>
       <c r="C24" s="2">
-        <v>25332</v>
+        <v>25290</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1964,10 +2369,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C25" s="2">
-        <v>3766</v>
+        <v>3765</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1975,10 +2380,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C26" s="2">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -1986,10 +2391,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C27" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -1997,10 +2402,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>2097</v>
+        <v>2107</v>
       </c>
       <c r="C28" s="2">
-        <v>17432</v>
+        <v>17519</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2008,10 +2413,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1129</v>
+        <v>1139</v>
       </c>
       <c r="C29" s="2">
-        <v>15466</v>
+        <v>15441</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2030,10 +2435,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C31" s="2">
-        <v>3403</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2041,10 +2446,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C32" s="2">
-        <v>4005</v>
+        <v>4004</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -2052,10 +2457,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C33" s="2">
-        <v>6094</v>
+        <v>6074</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2063,10 +2468,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C34" s="2">
-        <v>3501</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2085,10 +2490,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>13343</v>
+        <v>13483</v>
       </c>
       <c r="C36" s="2">
-        <v>152356</v>
+        <v>152361</v>
       </c>
     </row>
   </sheetData>
@@ -2167,10 +2572,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C7" s="2">
-        <v>2654</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2189,10 +2594,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C9" s="2">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2244,10 +2649,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C14" s="2">
-        <v>2722</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2299,10 +2704,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="C19" s="2">
-        <v>1821</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2310,10 +2715,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C20" s="2">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2321,10 +2726,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>863</v>
+        <v>879</v>
       </c>
       <c r="C21" s="2">
-        <v>7926</v>
+        <v>8066</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2332,10 +2737,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>602</v>
+        <v>615</v>
       </c>
       <c r="C22" s="2">
-        <v>3539</v>
+        <v>3559</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2343,10 +2748,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C23" s="2">
-        <v>16524</v>
+        <v>16525</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2354,10 +2759,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1736</v>
+        <v>1774</v>
       </c>
       <c r="C24" s="2">
-        <v>20675</v>
+        <v>20681</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2365,7 +2770,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C25" s="2">
         <v>2699</v>
@@ -2376,10 +2781,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C26" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -2387,10 +2792,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C27" s="2">
-        <v>586</v>
+        <v>581</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -2398,10 +2803,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1502</v>
+        <v>1512</v>
       </c>
       <c r="C28" s="2">
-        <v>12463</v>
+        <v>12549</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2409,10 +2814,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>944</v>
+        <v>955</v>
       </c>
       <c r="C29" s="2">
-        <v>10933</v>
+        <v>10926</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2431,10 +2836,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C31" s="2">
-        <v>1844</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2442,7 +2847,7 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C32" s="2">
         <v>2218</v>
@@ -2453,10 +2858,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C33" s="2">
-        <v>2952</v>
+        <v>2954</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2464,10 +2869,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C34" s="2">
-        <v>2529</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2486,10 +2891,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>10021</v>
+        <v>10147</v>
       </c>
       <c r="C36" s="2">
-        <v>104230</v>
+        <v>104462</v>
       </c>
     </row>
   </sheetData>
@@ -2568,10 +2973,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2">
-        <v>1849</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2590,10 +2995,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C9" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2645,10 +3050,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C14" s="2">
-        <v>2324</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2700,10 +3105,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="C19" s="2">
-        <v>1506</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2711,10 +3116,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C20" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2722,10 +3127,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>716</v>
+        <v>728</v>
       </c>
       <c r="C21" s="2">
-        <v>6613</v>
+        <v>6733</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2733,10 +3138,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="C22" s="2">
-        <v>2844</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2744,10 +3149,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C23" s="2">
-        <v>16195</v>
+        <v>16192</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -2755,10 +3160,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1509</v>
+        <v>1542</v>
       </c>
       <c r="C24" s="2">
-        <v>18576</v>
+        <v>18603</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2766,10 +3171,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C25" s="2">
-        <v>2349</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -2777,10 +3182,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C26" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -2788,7 +3193,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C27" s="2">
         <v>499</v>
@@ -2799,10 +3204,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1259</v>
+        <v>1266</v>
       </c>
       <c r="C28" s="2">
-        <v>10105</v>
+        <v>10085</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2810,7 +3215,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="C29" s="2">
         <v>9748</v>
@@ -2832,10 +3237,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C31" s="2">
-        <v>1509</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2843,7 +3248,7 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C32" s="2">
         <v>1611</v>
@@ -2854,10 +3259,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C33" s="2">
-        <v>2213</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2865,10 +3270,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C34" s="2">
-        <v>2049</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2887,10 +3292,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>8500</v>
+        <v>8611</v>
       </c>
       <c r="C36" s="2">
-        <v>90090</v>
+        <v>90194</v>
       </c>
     </row>
   </sheetData>
@@ -2991,10 +3396,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C9" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -3024,10 +3429,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C12" s="2">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -3046,10 +3451,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C14" s="2">
-        <v>2405</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -3101,10 +3506,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="C19" s="2">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -3112,10 +3517,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C20" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -3123,10 +3528,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="C21" s="2">
-        <v>3954</v>
+        <v>3977</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3134,10 +3539,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="C22" s="2">
-        <v>2093</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3145,10 +3550,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C23" s="2">
-        <v>14492</v>
+        <v>15442</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -3156,10 +3561,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1106</v>
+        <v>1138</v>
       </c>
       <c r="C24" s="2">
-        <v>14775</v>
+        <v>14765</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -3167,10 +3572,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C25" s="2">
-        <v>1714</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -3178,7 +3583,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C26" s="2">
         <v>435</v>
@@ -3189,7 +3594,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C27" s="2">
         <v>196</v>
@@ -3200,10 +3605,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>842</v>
+        <v>856</v>
       </c>
       <c r="C28" s="2">
-        <v>7041</v>
+        <v>7090</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -3211,10 +3616,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="C29" s="2">
-        <v>7747</v>
+        <v>7760</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -3244,10 +3649,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C32" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -3255,10 +3660,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C33" s="2">
-        <v>1377</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -3266,10 +3671,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="C34" s="2">
-        <v>1302</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -3288,10 +3693,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>5774</v>
+        <v>5903</v>
       </c>
       <c r="C36" s="2">
-        <v>67956</v>
+        <v>69189</v>
       </c>
     </row>
   </sheetData>
@@ -3370,10 +3775,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C7" s="2">
-        <v>1424</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -3425,10 +3830,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C12" s="2">
-        <v>1354</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -3447,10 +3852,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C14" s="2">
-        <v>1758</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -3469,10 +3874,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C16" s="2">
-        <v>1452</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -3502,10 +3907,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C19" s="2">
-        <v>1105</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -3513,10 +3918,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C20" s="2">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -3524,10 +3929,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="C21" s="2">
-        <v>3923</v>
+        <v>3753</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3535,10 +3940,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="C22" s="2">
-        <v>1843</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3546,7 +3951,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C23" s="2">
         <v>14580</v>
@@ -3557,10 +3962,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1247</v>
+        <v>1287</v>
       </c>
       <c r="C24" s="2">
-        <v>15973</v>
+        <v>15499</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -3568,7 +3973,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C25" s="2">
         <v>1810</v>
@@ -3579,10 +3984,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C26" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -3590,7 +3995,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C27" s="2">
         <v>168</v>
@@ -3601,7 +4006,7 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>805</v>
+        <v>819</v>
       </c>
       <c r="C28" s="2">
         <v>6396</v>
@@ -3612,10 +4017,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>633</v>
+        <v>644</v>
       </c>
       <c r="C29" s="2">
-        <v>7835</v>
+        <v>7814</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -3634,10 +4039,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C31" s="2">
-        <v>910</v>
+        <v>907</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -3645,10 +4050,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C32" s="2">
-        <v>774</v>
+        <v>748</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -3656,10 +4061,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C33" s="2">
-        <v>1557</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -3667,10 +4072,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="C34" s="2">
-        <v>1376</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -3689,10 +4094,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>5994</v>
+        <v>6133</v>
       </c>
       <c r="C36" s="2">
-        <v>68078</v>
+        <v>67432</v>
       </c>
     </row>
   </sheetData>
@@ -3771,10 +4176,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C7" s="2">
-        <v>1815</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -3782,10 +4187,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -3796,7 +4201,7 @@
         <v>103</v>
       </c>
       <c r="C9" s="2">
-        <v>548</v>
+        <v>544</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -3804,10 +4209,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -3815,7 +4220,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" s="2">
         <v>115</v>
@@ -3826,10 +4231,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2">
-        <v>1234</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -3837,10 +4242,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C13" s="2">
-        <v>1236</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -3848,10 +4253,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C14" s="2">
-        <v>2077</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -3870,10 +4275,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C16" s="2">
-        <v>1479</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -3903,10 +4308,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="C19" s="2">
-        <v>1387</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -3914,10 +4319,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="C20" s="2">
-        <v>475</v>
+        <v>483</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -3925,10 +4330,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>561</v>
+        <v>576</v>
       </c>
       <c r="C21" s="2">
-        <v>4334</v>
+        <v>4576</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3936,10 +4341,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>466</v>
+        <v>487</v>
       </c>
       <c r="C22" s="2">
-        <v>2570</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3947,10 +4352,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="C23" s="2">
-        <v>14398</v>
+        <v>14452</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -3958,10 +4363,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1808</v>
+        <v>1888</v>
       </c>
       <c r="C24" s="2">
-        <v>20780</v>
+        <v>20858</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -3969,10 +4374,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2">
-        <v>1909</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -3980,10 +4385,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C26" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -3991,10 +4396,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C27" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -4002,10 +4407,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>989</v>
+        <v>1012</v>
       </c>
       <c r="C28" s="2">
-        <v>8583</v>
+        <v>8731</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -4013,10 +4418,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>683</v>
+        <v>705</v>
       </c>
       <c r="C29" s="2">
-        <v>8407</v>
+        <v>8484</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -4035,10 +4440,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C31" s="2">
-        <v>1025</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -4046,10 +4451,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C32" s="2">
-        <v>1050</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -4057,10 +4462,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="C33" s="2">
-        <v>4374</v>
+        <v>4415</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -4068,10 +4473,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>730</v>
+        <v>743</v>
       </c>
       <c r="C34" s="2">
-        <v>1945</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -4090,10 +4495,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>7468</v>
+        <v>7736</v>
       </c>
       <c r="C36" s="2">
-        <v>81502</v>
+        <v>82111</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Ausz KonPe KTZH.xlsx
+++ b/KAE Ausz KonPe KTZH.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" firstSheet="6" activeTab="9"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" firstSheet="3" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="März 2020" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Oktober 2020" sheetId="8" r:id="rId8"/>
     <sheet name="November 2020" sheetId="9" r:id="rId9"/>
     <sheet name="Dezember 2020" sheetId="10" r:id="rId10"/>
+    <sheet name="Januar 2021" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="50">
   <si>
     <t>Metriken</t>
   </si>
@@ -181,6 +182,9 @@
   <si>
     <t>Dezember 2020</t>
   </si>
+  <si>
+    <t>Januar 2021</t>
+  </si>
 </sst>
 </file>
 
@@ -214,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -227,6 +231,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -701,10 +708,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C19" s="2">
-        <v>3592</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -712,7 +719,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="C20" s="2">
         <v>3565</v>
@@ -723,10 +730,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1347</v>
+        <v>1352</v>
       </c>
       <c r="C21" s="2">
-        <v>10031</v>
+        <v>10011</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -734,10 +741,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1951</v>
+        <v>1955</v>
       </c>
       <c r="C22" s="2">
-        <v>12216</v>
+        <v>12224</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -756,7 +763,7 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3314</v>
+        <v>3326</v>
       </c>
       <c r="C24" s="2">
         <v>34223</v>
@@ -767,7 +774,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C25" s="2">
         <v>2413</v>
@@ -800,10 +807,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>2531</v>
+        <v>2536</v>
       </c>
       <c r="C28" s="2">
-        <v>20954</v>
+        <v>21166</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -811,10 +818,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="C29" s="2">
-        <v>23527</v>
+        <v>23545</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -833,10 +840,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C31" s="2">
-        <v>6501</v>
+        <v>6499</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -844,10 +851,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="C32" s="2">
-        <v>12435</v>
+        <v>12379</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -855,10 +862,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="C33" s="2">
-        <v>9903</v>
+        <v>9906</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -866,10 +873,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="C34" s="2">
-        <v>6657</v>
+        <v>6658</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -888,10 +895,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>20158</v>
+        <v>20202</v>
       </c>
       <c r="C36" s="2">
-        <v>176859</v>
+        <v>176971</v>
       </c>
     </row>
   </sheetData>
@@ -970,10 +977,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C7" s="2">
-        <v>2456</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -992,10 +999,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C9" s="2">
-        <v>502</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1025,10 +1032,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C12" s="2">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1036,10 +1043,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C13" s="2">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1069,10 +1076,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C16" s="2">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1102,10 +1109,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="C19" s="2">
-        <v>1385</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1113,10 +1120,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2">
-        <v>448</v>
+        <v>483</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1124,10 +1131,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>492</v>
+        <v>532</v>
       </c>
       <c r="C21" s="2">
-        <v>4264</v>
+        <v>4454</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1135,10 +1142,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>483</v>
+        <v>522</v>
       </c>
       <c r="C22" s="2">
-        <v>2779</v>
+        <v>3309</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1146,10 +1153,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="C23" s="2">
-        <v>14391</v>
+        <v>14597</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1157,10 +1164,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2084</v>
+        <v>2264</v>
       </c>
       <c r="C24" s="2">
-        <v>23644</v>
+        <v>24222</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1168,10 +1175,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="C25" s="2">
-        <v>1422</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1179,10 +1186,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C26" s="2">
-        <v>349</v>
+        <v>385</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -1190,10 +1197,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C27" s="2">
-        <v>332</v>
+        <v>399</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -1201,10 +1208,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>875</v>
+        <v>927</v>
       </c>
       <c r="C28" s="2">
-        <v>7655</v>
+        <v>7978</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1212,10 +1219,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>632</v>
+        <v>672</v>
       </c>
       <c r="C29" s="2">
-        <v>8591</v>
+        <v>8708</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1234,10 +1241,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="C31" s="2">
-        <v>1333</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1245,10 +1252,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="C32" s="2">
-        <v>1235</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1256,10 +1263,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>452</v>
+        <v>496</v>
       </c>
       <c r="C33" s="2">
-        <v>6929</v>
+        <v>7272</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1267,10 +1274,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>349</v>
+        <v>386</v>
       </c>
       <c r="C34" s="2">
-        <v>1904</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1289,10 +1296,411 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>7391</v>
+        <v>7967</v>
       </c>
       <c r="C36" s="2">
-        <v>85740</v>
+        <v>88664</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="58.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>219</v>
+      </c>
+      <c r="C7" s="2">
+        <v>3482</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>67</v>
+      </c>
+      <c r="C8" s="2">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>123</v>
+      </c>
+      <c r="C9" s="2">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>106</v>
+      </c>
+      <c r="C12" s="2">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>66</v>
+      </c>
+      <c r="C13" s="2">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>79</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>79</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2">
+        <v>443</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2">
+        <v>279</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2">
+        <v>754</v>
+      </c>
+      <c r="C21" s="2">
+        <v>6428</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1127</v>
+      </c>
+      <c r="C22" s="2">
+        <v>7291</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2">
+        <v>319</v>
+      </c>
+      <c r="C23" s="2">
+        <v>14127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2">
+        <v>2499</v>
+      </c>
+      <c r="C24" s="2">
+        <v>21899</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2">
+        <v>159</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2">
+        <v>95</v>
+      </c>
+      <c r="C26" s="2">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2">
+        <v>85</v>
+      </c>
+      <c r="C27" s="2">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2">
+        <v>1318</v>
+      </c>
+      <c r="C28" s="2">
+        <v>13850</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2">
+        <v>764</v>
+      </c>
+      <c r="C29" s="2">
+        <v>10372</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2">
+        <v>256</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="2">
+        <v>262</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2">
+        <v>600</v>
+      </c>
+      <c r="C33" s="2">
+        <v>8801</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="2">
+        <v>475</v>
+      </c>
+      <c r="C34" s="2">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="2">
+        <v>10243</v>
+      </c>
+      <c r="C36" s="2">
+        <v>104127</v>
       </c>
     </row>
   </sheetData>
@@ -1504,7 +1912,7 @@
         <v>1399</v>
       </c>
       <c r="C19" s="2">
-        <v>7022</v>
+        <v>6999</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1512,10 +1920,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="C20" s="2">
-        <v>5880</v>
+        <v>5877</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1523,10 +1931,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="C21" s="2">
-        <v>19352</v>
+        <v>19345</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1534,10 +1942,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>2158</v>
+        <v>2166</v>
       </c>
       <c r="C22" s="2">
-        <v>14370</v>
+        <v>14386</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1545,10 +1953,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C23" s="2">
-        <v>20190</v>
+        <v>20200</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1556,10 +1964,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3301</v>
+        <v>3317</v>
       </c>
       <c r="C24" s="2">
-        <v>36222</v>
+        <v>36229</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1567,7 +1975,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C25" s="2">
         <v>5559</v>
@@ -1600,10 +2008,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>3759</v>
+        <v>3758</v>
       </c>
       <c r="C28" s="2">
-        <v>32964</v>
+        <v>32957</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1611,10 +2019,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1801</v>
+        <v>1805</v>
       </c>
       <c r="C29" s="2">
-        <v>31763</v>
+        <v>31761</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1633,10 +2041,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C31" s="2">
-        <v>8119</v>
+        <v>8118</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1644,10 +2052,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>2914</v>
+        <v>2917</v>
       </c>
       <c r="C32" s="2">
-        <v>22003</v>
+        <v>21942</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1655,10 +2063,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="C33" s="2">
-        <v>11911</v>
+        <v>11939</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1666,10 +2074,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>1715</v>
+        <v>1718</v>
       </c>
       <c r="C34" s="2">
-        <v>8391</v>
+        <v>8393</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1688,10 +2096,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>25860</v>
+        <v>25907</v>
       </c>
       <c r="C36" s="2">
-        <v>253903</v>
+        <v>253580</v>
       </c>
     </row>
   </sheetData>
@@ -1902,10 +2310,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="C19" s="2">
-        <v>5683</v>
+        <v>5682</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1913,10 +2321,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="C20" s="2">
-        <v>4086</v>
+        <v>4089</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1924,10 +2332,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1823</v>
+        <v>1831</v>
       </c>
       <c r="C21" s="2">
-        <v>17747</v>
+        <v>17750</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1935,10 +2343,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1798</v>
+        <v>1805</v>
       </c>
       <c r="C22" s="2">
-        <v>11922</v>
+        <v>11934</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1957,10 +2365,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3052</v>
+        <v>3068</v>
       </c>
       <c r="C24" s="2">
-        <v>34481</v>
+        <v>34490</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1968,7 +2376,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C25" s="2">
         <v>5570</v>
@@ -2001,10 +2409,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>3618</v>
+        <v>3620</v>
       </c>
       <c r="C28" s="2">
-        <v>29298</v>
+        <v>29438</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2012,10 +2420,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1642</v>
+        <v>1648</v>
       </c>
       <c r="C29" s="2">
-        <v>21167</v>
+        <v>21218</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2034,10 +2442,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C31" s="2">
-        <v>6871</v>
+        <v>6882</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2045,10 +2453,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="C32" s="2">
-        <v>10091</v>
+        <v>10093</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -2056,10 +2464,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="C33" s="2">
-        <v>11407</v>
+        <v>11441</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2067,10 +2475,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="C34" s="2">
-        <v>5692</v>
+        <v>5693</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2089,10 +2497,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>21892</v>
+        <v>21942</v>
       </c>
       <c r="C36" s="2">
-        <v>215071</v>
+        <v>215008</v>
       </c>
     </row>
   </sheetData>
@@ -2237,10 +2645,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C13" s="2">
-        <v>5774</v>
+        <v>5775</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2303,10 +2711,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C19" s="2">
-        <v>2715</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2314,10 +2722,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="C20" s="2">
-        <v>1484</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2325,7 +2733,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1170</v>
+        <v>1178</v>
       </c>
       <c r="C21" s="2">
         <v>11130</v>
@@ -2336,10 +2744,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="C22" s="2">
-        <v>5529</v>
+        <v>5533</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2358,10 +2766,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2245</v>
+        <v>2262</v>
       </c>
       <c r="C24" s="2">
-        <v>25290</v>
+        <v>25287</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2369,7 +2777,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C25" s="2">
         <v>3765</v>
@@ -2380,10 +2788,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C26" s="2">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -2391,10 +2799,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C27" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -2402,10 +2810,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>2107</v>
+        <v>2118</v>
       </c>
       <c r="C28" s="2">
-        <v>17519</v>
+        <v>17650</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2413,10 +2821,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="C29" s="2">
-        <v>15441</v>
+        <v>15431</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2435,10 +2843,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C31" s="2">
-        <v>3405</v>
+        <v>3402</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2457,10 +2865,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C33" s="2">
-        <v>6074</v>
+        <v>6091</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2468,7 +2876,7 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C34" s="2">
         <v>3498</v>
@@ -2490,10 +2898,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>13483</v>
+        <v>13539</v>
       </c>
       <c r="C36" s="2">
-        <v>152361</v>
+        <v>152152</v>
       </c>
     </row>
   </sheetData>
@@ -2638,10 +3046,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C13" s="2">
-        <v>3794</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2704,10 +3112,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C19" s="2">
-        <v>1811</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2715,10 +3123,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C20" s="2">
-        <v>843</v>
+        <v>837</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2726,10 +3134,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="C21" s="2">
-        <v>8066</v>
+        <v>8060</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2737,10 +3145,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="C22" s="2">
-        <v>3559</v>
+        <v>3556</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2759,10 +3167,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1774</v>
+        <v>1790</v>
       </c>
       <c r="C24" s="2">
-        <v>20681</v>
+        <v>20677</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2770,7 +3178,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C25" s="2">
         <v>2699</v>
@@ -2781,10 +3189,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C26" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -2803,10 +3211,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1512</v>
+        <v>1519</v>
       </c>
       <c r="C28" s="2">
-        <v>12549</v>
+        <v>12656</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2814,10 +3222,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="C29" s="2">
-        <v>10926</v>
+        <v>10910</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2836,10 +3244,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C31" s="2">
-        <v>1843</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2847,7 +3255,7 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C32" s="2">
         <v>2218</v>
@@ -2858,10 +3266,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C33" s="2">
-        <v>2954</v>
+        <v>2953</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2869,7 +3277,7 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C34" s="2">
         <v>2528</v>
@@ -2891,10 +3299,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>10147</v>
+        <v>10194</v>
       </c>
       <c r="C36" s="2">
-        <v>104462</v>
+        <v>104241</v>
       </c>
     </row>
   </sheetData>
@@ -3039,10 +3447,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2">
-        <v>2742</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -3105,10 +3513,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C19" s="2">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -3116,10 +3524,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C20" s="2">
-        <v>737</v>
+        <v>731</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -3127,10 +3535,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="C21" s="2">
-        <v>6733</v>
+        <v>6729</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3138,10 +3546,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="C22" s="2">
-        <v>2834</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3160,7 +3568,7 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1542</v>
+        <v>1555</v>
       </c>
       <c r="C24" s="2">
         <v>18603</v>
@@ -3171,10 +3579,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C25" s="2">
-        <v>2350</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -3182,10 +3590,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C26" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -3204,10 +3612,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="C28" s="2">
-        <v>10085</v>
+        <v>10193</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -3215,10 +3623,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="C29" s="2">
-        <v>9748</v>
+        <v>9733</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -3237,10 +3645,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C31" s="2">
-        <v>1508</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -3248,10 +3656,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C32" s="2">
-        <v>1611</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -3259,10 +3667,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C33" s="2">
-        <v>2208</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -3270,10 +3678,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C34" s="2">
-        <v>2048</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -3292,10 +3700,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>8611</v>
+        <v>8660</v>
       </c>
       <c r="C36" s="2">
-        <v>90194</v>
+        <v>90038</v>
       </c>
     </row>
   </sheetData>
@@ -3407,7 +3815,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="2">
         <v>186</v>
@@ -3432,7 +3840,7 @@
         <v>101</v>
       </c>
       <c r="C12" s="2">
-        <v>1177</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -3473,10 +3881,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C16" s="2">
-        <v>1559</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -3506,10 +3914,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C19" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -3517,10 +3925,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C20" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -3528,10 +3936,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C21" s="2">
-        <v>3977</v>
+        <v>3790</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3539,10 +3947,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C22" s="2">
-        <v>2089</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3550,10 +3958,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C23" s="2">
-        <v>15442</v>
+        <v>15438</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -3561,10 +3969,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1138</v>
+        <v>1159</v>
       </c>
       <c r="C24" s="2">
-        <v>14765</v>
+        <v>14259</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -3572,10 +3980,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C25" s="2">
-        <v>1918</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -3583,10 +3991,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C26" s="2">
-        <v>435</v>
+        <v>457</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -3605,10 +4013,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>856</v>
+        <v>869</v>
       </c>
       <c r="C28" s="2">
-        <v>7090</v>
+        <v>7108</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -3616,10 +4024,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C29" s="2">
-        <v>7760</v>
+        <v>7745</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -3649,10 +4057,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C32" s="2">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -3660,10 +4068,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C33" s="2">
-        <v>1379</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -3671,10 +4079,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="C34" s="2">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -3693,10 +4101,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>5903</v>
+        <v>5976</v>
       </c>
       <c r="C36" s="2">
-        <v>69189</v>
+        <v>68546</v>
       </c>
     </row>
   </sheetData>
@@ -3775,10 +4183,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C7" s="2">
-        <v>1427</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -3800,7 +4208,7 @@
         <v>106</v>
       </c>
       <c r="C9" s="2">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -3874,7 +4282,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C16" s="2">
         <v>1458</v>
@@ -3907,10 +4315,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C19" s="2">
-        <v>1117</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -3918,10 +4326,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C20" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -3929,10 +4337,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="C21" s="2">
-        <v>3753</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3940,10 +4348,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="C22" s="2">
-        <v>1835</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3951,10 +4359,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C23" s="2">
-        <v>14580</v>
+        <v>14569</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -3962,10 +4370,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1287</v>
+        <v>1311</v>
       </c>
       <c r="C24" s="2">
-        <v>15499</v>
+        <v>15304</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -3973,10 +4381,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C25" s="2">
-        <v>1810</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -3984,10 +4392,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C26" s="2">
-        <v>415</v>
+        <v>436</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -3998,7 +4406,7 @@
         <v>44</v>
       </c>
       <c r="C27" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -4006,10 +4414,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>819</v>
+        <v>831</v>
       </c>
       <c r="C28" s="2">
-        <v>6396</v>
+        <v>6332</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -4017,10 +4425,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="C29" s="2">
-        <v>7814</v>
+        <v>7783</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -4039,7 +4447,7 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C31" s="2">
         <v>907</v>
@@ -4050,10 +4458,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C32" s="2">
-        <v>748</v>
+        <v>756</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -4061,10 +4469,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C33" s="2">
-        <v>1560</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -4072,10 +4480,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="C34" s="2">
-        <v>1382</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -4094,10 +4502,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>6133</v>
+        <v>6218</v>
       </c>
       <c r="C36" s="2">
-        <v>67432</v>
+        <v>66879</v>
       </c>
     </row>
   </sheetData>
@@ -4176,10 +4584,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C7" s="2">
-        <v>1758</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -4198,10 +4606,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2">
-        <v>544</v>
+        <v>551</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -4223,7 +4631,7 @@
         <v>17</v>
       </c>
       <c r="C11" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -4231,10 +4639,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2">
-        <v>1237</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -4275,7 +4683,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C16" s="2">
         <v>1483</v>
@@ -4308,10 +4716,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C19" s="2">
-        <v>1401</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -4319,10 +4727,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -4330,10 +4738,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>576</v>
-      </c>
-      <c r="C21" s="2">
-        <v>4576</v>
+        <v>586</v>
+      </c>
+      <c r="C21" s="6">
+        <v>6117.8</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -4341,10 +4749,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="C22" s="2">
-        <v>2706</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -4352,10 +4760,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C23" s="2">
-        <v>14452</v>
+        <v>14482</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -4363,10 +4771,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1888</v>
-      </c>
-      <c r="C24" s="2">
-        <v>20858</v>
+        <v>1930</v>
+      </c>
+      <c r="C24" s="6">
+        <v>23521.8</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -4374,10 +4782,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2">
-        <v>1877</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -4385,10 +4793,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>104</v>
-      </c>
-      <c r="C26" s="2">
-        <v>418</v>
+        <v>106</v>
+      </c>
+      <c r="C26" s="6">
+        <v>3297.8</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -4399,7 +4807,7 @@
         <v>63</v>
       </c>
       <c r="C27" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -4407,10 +4815,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1012</v>
+        <v>1036</v>
       </c>
       <c r="C28" s="2">
-        <v>8731</v>
+        <v>9064</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -4418,10 +4826,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="C29" s="2">
-        <v>8484</v>
+        <v>8493</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -4440,10 +4848,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="C31" s="2">
-        <v>1021</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -4451,10 +4859,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C32" s="2">
-        <v>1122</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -4462,10 +4870,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="C33" s="2">
-        <v>4415</v>
+        <v>4563</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -4473,10 +4881,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="C34" s="2">
-        <v>1976</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -4495,10 +4903,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>7736</v>
-      </c>
-      <c r="C36" s="2">
-        <v>82111</v>
+        <v>7888</v>
+      </c>
+      <c r="C36" s="6">
+        <v>90456.400000000009</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Ausz KonPe KTZH.xlsx
+++ b/KAE Ausz KonPe KTZH.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" firstSheet="3" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" firstSheet="9" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="März 2020" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="November 2020" sheetId="9" r:id="rId9"/>
     <sheet name="Dezember 2020" sheetId="10" r:id="rId10"/>
     <sheet name="Januar 2021" sheetId="11" r:id="rId11"/>
+    <sheet name="Februar 2021" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="51">
   <si>
     <t>Metriken</t>
   </si>
@@ -184,6 +185,9 @@
   </si>
   <si>
     <t>Januar 2021</t>
+  </si>
+  <si>
+    <t>Februar 2021</t>
   </si>
 </sst>
 </file>
@@ -576,7 +580,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C7" s="2">
         <v>4461</v>
@@ -708,7 +712,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C19" s="2">
         <v>3571</v>
@@ -719,7 +723,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="C20" s="2">
         <v>3565</v>
@@ -730,10 +734,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="C21" s="2">
-        <v>10011</v>
+        <v>9812</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -741,10 +745,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1955</v>
+        <v>1959</v>
       </c>
       <c r="C22" s="2">
-        <v>12224</v>
+        <v>12423</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -763,10 +767,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3326</v>
+        <v>3342</v>
       </c>
       <c r="C24" s="2">
-        <v>34223</v>
+        <v>34222</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -785,7 +789,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C26" s="2">
         <v>1247</v>
@@ -807,10 +811,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>2536</v>
+        <v>2541</v>
       </c>
       <c r="C28" s="2">
-        <v>21166</v>
+        <v>21175</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -818,7 +822,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="C29" s="2">
         <v>23545</v>
@@ -840,7 +844,7 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="C31" s="2">
         <v>6499</v>
@@ -862,7 +866,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C33" s="2">
         <v>9906</v>
@@ -873,10 +877,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>1611</v>
+        <v>1615</v>
       </c>
       <c r="C34" s="2">
-        <v>6658</v>
+        <v>6662</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -895,10 +899,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>20202</v>
+        <v>20243</v>
       </c>
       <c r="C36" s="2">
-        <v>176971</v>
+        <v>176983</v>
       </c>
     </row>
   </sheetData>
@@ -977,10 +981,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C7" s="2">
-        <v>2512</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -999,7 +1003,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C9" s="2">
         <v>511</v>
@@ -1032,10 +1036,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C12" s="2">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1043,10 +1047,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C13" s="2">
-        <v>1307</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1054,10 +1058,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C14" s="2">
-        <v>1189</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1109,10 +1113,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="C19" s="2">
-        <v>1464</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1120,10 +1124,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C20" s="2">
-        <v>483</v>
+        <v>504</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1131,10 +1135,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="C21" s="2">
-        <v>4454</v>
+        <v>4547</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1142,10 +1146,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="C22" s="2">
-        <v>3309</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1153,10 +1157,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="C23" s="2">
-        <v>14597</v>
+        <v>14626</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1164,10 +1168,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2264</v>
+        <v>2356</v>
       </c>
       <c r="C24" s="2">
-        <v>24222</v>
+        <v>24446</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1175,10 +1179,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C25" s="2">
-        <v>1444</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1186,10 +1190,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C26" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -1197,10 +1201,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C27" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -1208,10 +1212,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>927</v>
+        <v>957</v>
       </c>
       <c r="C28" s="2">
-        <v>7978</v>
+        <v>8128</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1219,10 +1223,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>672</v>
+        <v>689</v>
       </c>
       <c r="C29" s="2">
-        <v>8708</v>
+        <v>8824</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1241,10 +1245,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="C31" s="2">
-        <v>1397</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1252,10 +1256,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="C32" s="2">
-        <v>1304</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1263,10 +1267,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="C33" s="2">
-        <v>7272</v>
+        <v>7347</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1274,10 +1278,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="C34" s="2">
-        <v>2093</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1296,10 +1300,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>7967</v>
+        <v>8251</v>
       </c>
       <c r="C36" s="2">
-        <v>88664</v>
+        <v>89581</v>
       </c>
     </row>
   </sheetData>
@@ -1356,7 +1360,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="2">
         <v>163</v>
@@ -1378,10 +1382,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C7" s="2">
-        <v>3482</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1389,10 +1393,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>67</v>
+        <v>195</v>
       </c>
       <c r="C8" s="2">
-        <v>415</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1400,10 +1404,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C9" s="2">
-        <v>888</v>
+        <v>893</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1433,10 +1437,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C12" s="2">
-        <v>992</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1444,10 +1448,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C13" s="2">
-        <v>799</v>
+        <v>907</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1455,10 +1459,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C14" s="2">
-        <v>1498</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1477,10 +1481,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C16" s="2">
-        <v>1484</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1510,10 +1514,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="C19" s="2">
-        <v>1984</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1521,10 +1525,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="C20" s="2">
-        <v>1171</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1532,10 +1536,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>754</v>
+        <v>875</v>
       </c>
       <c r="C21" s="2">
-        <v>6428</v>
+        <v>7222</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1543,10 +1547,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1127</v>
+        <v>1286</v>
       </c>
       <c r="C22" s="2">
-        <v>7291</v>
+        <v>8559</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1554,10 +1558,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="C23" s="2">
-        <v>14127</v>
+        <v>14170</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1565,10 +1569,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2499</v>
+        <v>2616</v>
       </c>
       <c r="C24" s="2">
-        <v>21899</v>
+        <v>22516</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1576,10 +1580,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C25" s="2">
-        <v>1480</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1587,10 +1591,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C26" s="2">
-        <v>456</v>
+        <v>469</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -1598,10 +1602,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C27" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -1609,10 +1613,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1318</v>
+        <v>1414</v>
       </c>
       <c r="C28" s="2">
-        <v>13850</v>
+        <v>15850</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1620,10 +1624,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>764</v>
+        <v>788</v>
       </c>
       <c r="C29" s="2">
-        <v>10372</v>
+        <v>10563</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1642,10 +1646,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="C31" s="2">
-        <v>1691</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1653,10 +1657,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>262</v>
+        <v>293</v>
       </c>
       <c r="C32" s="2">
-        <v>1594</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1664,10 +1668,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>600</v>
+        <v>634</v>
       </c>
       <c r="C33" s="2">
-        <v>8801</v>
+        <v>9059</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1675,10 +1679,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>475</v>
+        <v>512</v>
       </c>
       <c r="C34" s="2">
-        <v>2361</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1697,10 +1701,411 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>10243</v>
+        <v>11135</v>
       </c>
       <c r="C36" s="2">
-        <v>104127</v>
+        <v>111672</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="58.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>224</v>
+      </c>
+      <c r="C7" s="2">
+        <v>3470</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>60</v>
+      </c>
+      <c r="C8" s="2">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>130</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>107</v>
+      </c>
+      <c r="C12" s="2">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>62</v>
+      </c>
+      <c r="C13" s="2">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>64</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>94</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2">
+        <v>515</v>
+      </c>
+      <c r="C19" s="2">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2">
+        <v>338</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2">
+        <v>792</v>
+      </c>
+      <c r="C21" s="2">
+        <v>6565</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1210</v>
+      </c>
+      <c r="C22" s="2">
+        <v>7093</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2">
+        <v>336</v>
+      </c>
+      <c r="C23" s="2">
+        <v>14080</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2">
+        <v>2473</v>
+      </c>
+      <c r="C24" s="2">
+        <v>21351</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2">
+        <v>157</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2">
+        <v>114</v>
+      </c>
+      <c r="C26" s="2">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2">
+        <v>95</v>
+      </c>
+      <c r="C27" s="2">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2">
+        <v>1307</v>
+      </c>
+      <c r="C28" s="2">
+        <v>13232</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2">
+        <v>789</v>
+      </c>
+      <c r="C29" s="2">
+        <v>10621</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2">
+        <v>265</v>
+      </c>
+      <c r="C31" s="2">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="2">
+        <v>285</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2">
+        <v>598</v>
+      </c>
+      <c r="C33" s="2">
+        <v>8602</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="2">
+        <v>515</v>
+      </c>
+      <c r="C34" s="2">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="2">
+        <v>10607</v>
+      </c>
+      <c r="C36" s="2">
+        <v>103379</v>
       </c>
     </row>
   </sheetData>
@@ -1799,10 +2204,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C9" s="2">
-        <v>1958</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1854,10 +2259,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2">
-        <v>2949</v>
+        <v>2939</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1909,7 +2314,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="C19" s="2">
         <v>6999</v>
@@ -1920,7 +2325,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>999</v>
+        <v>1004</v>
       </c>
       <c r="C20" s="2">
         <v>5877</v>
@@ -1934,7 +2339,7 @@
         <v>2026</v>
       </c>
       <c r="C21" s="2">
-        <v>19345</v>
+        <v>19142</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1942,10 +2347,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>2166</v>
+        <v>2169</v>
       </c>
       <c r="C22" s="2">
-        <v>14386</v>
+        <v>14589</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1964,10 +2369,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3317</v>
+        <v>3340</v>
       </c>
       <c r="C24" s="2">
-        <v>36229</v>
+        <v>36235</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2011,7 +2416,7 @@
         <v>3758</v>
       </c>
       <c r="C28" s="2">
-        <v>32957</v>
+        <v>32958</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2019,10 +2424,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1805</v>
+        <v>1807</v>
       </c>
       <c r="C29" s="2">
-        <v>31761</v>
+        <v>31758</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2041,7 +2446,7 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="C31" s="2">
         <v>8118</v>
@@ -2063,7 +2468,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C33" s="2">
         <v>11939</v>
@@ -2074,10 +2479,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>1718</v>
+        <v>1724</v>
       </c>
       <c r="C34" s="2">
-        <v>8393</v>
+        <v>8397</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2096,10 +2501,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>25907</v>
+        <v>25954</v>
       </c>
       <c r="C36" s="2">
-        <v>253580</v>
+        <v>253579</v>
       </c>
     </row>
   </sheetData>
@@ -2178,10 +2583,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C7" s="2">
-        <v>5330</v>
+        <v>5331</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -2200,10 +2605,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C9" s="2">
-        <v>1963</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2255,7 +2660,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C14" s="2">
         <v>3514</v>
@@ -2310,7 +2715,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="C19" s="2">
         <v>5682</v>
@@ -2321,7 +2726,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C20" s="2">
         <v>4089</v>
@@ -2335,7 +2740,7 @@
         <v>1831</v>
       </c>
       <c r="C21" s="2">
-        <v>17750</v>
+        <v>17604</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2343,10 +2748,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1805</v>
+        <v>1808</v>
       </c>
       <c r="C22" s="2">
-        <v>11934</v>
+        <v>12080</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2354,7 +2759,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C23" s="2">
         <v>19455</v>
@@ -2365,10 +2770,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3068</v>
+        <v>3087</v>
       </c>
       <c r="C24" s="2">
-        <v>34490</v>
+        <v>34500</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2409,10 +2814,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>3620</v>
+        <v>3622</v>
       </c>
       <c r="C28" s="2">
-        <v>29438</v>
+        <v>29512</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2420,10 +2825,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1648</v>
+        <v>1650</v>
       </c>
       <c r="C29" s="2">
-        <v>21218</v>
+        <v>21215</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2442,7 +2847,7 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="C31" s="2">
         <v>6882</v>
@@ -2464,7 +2869,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C33" s="2">
         <v>11441</v>
@@ -2475,10 +2880,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="C34" s="2">
-        <v>5693</v>
+        <v>5698</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2497,10 +2902,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>21942</v>
+        <v>21983</v>
       </c>
       <c r="C36" s="2">
-        <v>215008</v>
+        <v>215096</v>
       </c>
     </row>
   </sheetData>
@@ -2579,7 +2984,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C7" s="2">
         <v>3679</v>
@@ -2656,10 +3061,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2">
-        <v>2888</v>
+        <v>2887</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -2711,10 +3116,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="C19" s="2">
-        <v>2712</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2722,10 +3127,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C20" s="2">
-        <v>1475</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2733,10 +3138,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C21" s="2">
-        <v>11130</v>
+        <v>10990</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2744,10 +3149,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="C22" s="2">
-        <v>5533</v>
+        <v>5672</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2766,7 +3171,7 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2262</v>
+        <v>2270</v>
       </c>
       <c r="C24" s="2">
         <v>25287</v>
@@ -2810,10 +3215,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="C28" s="2">
-        <v>17650</v>
+        <v>17723</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2821,10 +3226,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C29" s="2">
-        <v>15431</v>
+        <v>15430</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2843,10 +3248,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C31" s="2">
-        <v>3402</v>
+        <v>3401</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2876,10 +3281,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="C34" s="2">
-        <v>3498</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2898,10 +3303,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>13539</v>
+        <v>13573</v>
       </c>
       <c r="C36" s="2">
-        <v>152152</v>
+        <v>152218</v>
       </c>
     </row>
   </sheetData>
@@ -2980,7 +3385,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C7" s="2">
         <v>2658</v>
@@ -3057,10 +3462,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C14" s="2">
-        <v>2721</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -3079,10 +3484,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C16" s="2">
-        <v>1851</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -3112,10 +3517,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C19" s="2">
-        <v>1812</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -3123,7 +3528,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C20" s="2">
         <v>837</v>
@@ -3134,10 +3539,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C21" s="2">
-        <v>8060</v>
+        <v>7894</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3145,10 +3550,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="C22" s="2">
-        <v>3556</v>
+        <v>3726</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3156,10 +3561,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C23" s="2">
-        <v>16525</v>
+        <v>16524</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -3167,10 +3572,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1790</v>
+        <v>1795</v>
       </c>
       <c r="C24" s="2">
-        <v>20677</v>
+        <v>20681</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -3211,10 +3616,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1519</v>
+        <v>1526</v>
       </c>
       <c r="C28" s="2">
-        <v>12656</v>
+        <v>12738</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -3222,10 +3627,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C29" s="2">
-        <v>10910</v>
+        <v>10909</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -3244,10 +3649,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C31" s="2">
-        <v>1842</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -3277,10 +3682,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C34" s="2">
-        <v>2528</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -3299,10 +3704,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>10194</v>
+        <v>10227</v>
       </c>
       <c r="C36" s="2">
-        <v>104241</v>
+        <v>104353</v>
       </c>
     </row>
   </sheetData>
@@ -3381,10 +3786,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C7" s="2">
-        <v>1853</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -3458,10 +3863,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C14" s="2">
-        <v>2321</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -3513,7 +3918,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C19" s="2">
         <v>1500</v>
@@ -3524,7 +3929,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C20" s="2">
         <v>731</v>
@@ -3535,10 +3940,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C21" s="2">
-        <v>6729</v>
+        <v>6550</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3546,10 +3951,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="C22" s="2">
-        <v>2832</v>
+        <v>3014</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3557,10 +3962,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C23" s="2">
-        <v>16192</v>
+        <v>16191</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -3568,10 +3973,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1555</v>
+        <v>1561</v>
       </c>
       <c r="C24" s="2">
-        <v>18603</v>
+        <v>18605</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -3612,10 +4017,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1272</v>
+        <v>1279</v>
       </c>
       <c r="C28" s="2">
-        <v>10193</v>
+        <v>10270</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -3623,10 +4028,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C29" s="2">
-        <v>9733</v>
+        <v>9732</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -3645,10 +4050,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C31" s="2">
-        <v>1515</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -3656,10 +4061,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C32" s="2">
-        <v>1609</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -3678,10 +4083,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C34" s="2">
-        <v>2050</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -3700,10 +4105,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>8660</v>
+        <v>8693</v>
       </c>
       <c r="C36" s="2">
-        <v>90038</v>
+        <v>90112</v>
       </c>
     </row>
   </sheetData>
@@ -3782,10 +4187,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C7" s="2">
-        <v>1523</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -3804,10 +4209,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -3829,7 +4234,7 @@
         <v>17</v>
       </c>
       <c r="C11" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -3859,10 +4264,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C14" s="2">
-        <v>2404</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -3914,10 +4319,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C19" s="2">
-        <v>941</v>
+        <v>906</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -3928,7 +4333,7 @@
         <v>145</v>
       </c>
       <c r="C20" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -3936,10 +4341,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C21" s="2">
-        <v>3790</v>
+        <v>3918</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3947,10 +4352,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C22" s="2">
-        <v>2120</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3958,10 +4363,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C23" s="2">
-        <v>15438</v>
+        <v>15425</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -3969,10 +4374,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1159</v>
+        <v>1168</v>
       </c>
       <c r="C24" s="2">
-        <v>14259</v>
+        <v>14089</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -3980,10 +4385,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C25" s="2">
-        <v>1924</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -3991,7 +4396,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C26" s="2">
         <v>457</v>
@@ -4002,10 +4407,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C27" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -4013,10 +4418,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="C28" s="2">
-        <v>7108</v>
+        <v>7064</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -4024,10 +4429,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C29" s="2">
-        <v>7745</v>
+        <v>7729</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -4057,10 +4462,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C32" s="2">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -4068,10 +4473,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C33" s="2">
-        <v>1382</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -4079,10 +4484,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C34" s="2">
-        <v>1311</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -4101,10 +4506,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>5976</v>
+        <v>6027</v>
       </c>
       <c r="C36" s="2">
-        <v>68546</v>
+        <v>67960</v>
       </c>
     </row>
   </sheetData>
@@ -4186,7 +4591,7 @@
         <v>84</v>
       </c>
       <c r="C7" s="2">
-        <v>1355</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -4208,7 +4613,7 @@
         <v>106</v>
       </c>
       <c r="C9" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -4241,7 +4646,7 @@
         <v>100</v>
       </c>
       <c r="C12" s="2">
-        <v>1347</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -4260,10 +4665,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C14" s="2">
-        <v>1792</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -4315,10 +4720,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C19" s="2">
-        <v>1081</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -4329,7 +4734,7 @@
         <v>135</v>
       </c>
       <c r="C20" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -4337,10 +4742,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C21" s="2">
-        <v>3886</v>
+        <v>5397.8</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -4348,10 +4753,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C22" s="2">
-        <v>1790</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -4359,10 +4764,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C23" s="2">
-        <v>14569</v>
+        <v>14584</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -4370,10 +4775,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1311</v>
+        <v>1327</v>
       </c>
       <c r="C24" s="2">
-        <v>15304</v>
+        <v>17931.8</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -4381,10 +4786,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C25" s="2">
-        <v>1780</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -4392,10 +4797,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C26" s="2">
-        <v>436</v>
+        <v>3306.8</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -4403,10 +4808,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C27" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -4414,10 +4819,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="C28" s="2">
-        <v>6332</v>
+        <v>6573</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -4425,10 +4830,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C29" s="2">
-        <v>7783</v>
+        <v>7799</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -4447,10 +4852,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C31" s="2">
-        <v>907</v>
+        <v>916</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -4458,10 +4863,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C32" s="2">
-        <v>756</v>
+        <v>778</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -4469,10 +4874,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C33" s="2">
-        <v>1546</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -4480,10 +4885,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C34" s="2">
-        <v>1433</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -4502,10 +4907,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>6218</v>
+        <v>6270</v>
       </c>
       <c r="C36" s="2">
-        <v>66879</v>
+        <v>74692.399999999994</v>
       </c>
     </row>
   </sheetData>
@@ -4584,10 +4989,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C7" s="2">
-        <v>1837</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -4661,10 +5066,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C14" s="2">
-        <v>2111</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -4716,10 +5121,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="C19" s="2">
-        <v>1433</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -4727,10 +5132,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C20" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -4738,10 +5143,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C21" s="6">
-        <v>6117.8</v>
+        <v>4234.7</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -4749,10 +5154,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C22" s="2">
-        <v>2767</v>
+        <v>2952</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -4760,10 +5165,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C23" s="2">
-        <v>14482</v>
+        <v>14481</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -4771,10 +5176,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1930</v>
+        <v>1966</v>
       </c>
       <c r="C24" s="6">
-        <v>23521.8</v>
+        <v>21646</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -4793,10 +5198,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C26" s="6">
-        <v>3297.8</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -4804,10 +5209,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C27" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -4815,10 +5220,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1036</v>
+        <v>1047</v>
       </c>
       <c r="C28" s="2">
-        <v>9064</v>
+        <v>9142</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -4826,10 +5231,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C29" s="2">
-        <v>8493</v>
+        <v>8324.5499999999993</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -4848,10 +5253,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C31" s="2">
-        <v>1180</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -4859,10 +5264,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C32" s="2">
-        <v>1155</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -4870,10 +5275,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="C33" s="2">
-        <v>4563</v>
+        <v>4568</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -4881,10 +5286,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="C34" s="2">
-        <v>2027</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -4903,10 +5308,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>7888</v>
+        <v>7981</v>
       </c>
       <c r="C36" s="6">
-        <v>90456.400000000009</v>
+        <v>84857.25</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Ausz KonPe KTZH.xlsx
+++ b/KAE Ausz KonPe KTZH.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" firstSheet="9" activeTab="11"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895" firstSheet="5" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="März 2020" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="Dezember 2020" sheetId="10" r:id="rId10"/>
     <sheet name="Januar 2021" sheetId="11" r:id="rId11"/>
     <sheet name="Februar 2021" sheetId="12" r:id="rId12"/>
+    <sheet name="März 2021" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="52">
   <si>
     <t>Metriken</t>
   </si>
@@ -188,6 +189,9 @@
   </si>
   <si>
     <t>Februar 2021</t>
+  </si>
+  <si>
+    <t>März 2021</t>
   </si>
 </sst>
 </file>
@@ -580,7 +584,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C7" s="2">
         <v>4461</v>
@@ -602,10 +606,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C9" s="2">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -712,10 +716,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="C19" s="2">
-        <v>3571</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -723,10 +727,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C20" s="2">
-        <v>3565</v>
+        <v>3564</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -734,10 +738,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1351</v>
+        <v>1359</v>
       </c>
       <c r="C21" s="2">
-        <v>9812</v>
+        <v>9987</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -745,10 +749,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1959</v>
+        <v>1978</v>
       </c>
       <c r="C22" s="2">
-        <v>12423</v>
+        <v>12022</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -756,7 +760,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C23" s="2">
         <v>16048</v>
@@ -767,10 +771,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3342</v>
+        <v>3365</v>
       </c>
       <c r="C24" s="2">
-        <v>34222</v>
+        <v>34219</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -789,10 +793,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C26" s="2">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -811,10 +815,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>2541</v>
+        <v>2552</v>
       </c>
       <c r="C28" s="2">
-        <v>21175</v>
+        <v>21176</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -822,10 +826,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1309</v>
+        <v>1350</v>
       </c>
       <c r="C29" s="2">
-        <v>23545</v>
+        <v>23436</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -869,7 +873,7 @@
         <v>770</v>
       </c>
       <c r="C33" s="2">
-        <v>9906</v>
+        <v>9391</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -877,10 +881,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>1615</v>
+        <v>1620</v>
       </c>
       <c r="C34" s="2">
-        <v>6662</v>
+        <v>6655</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -899,10 +903,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>20243</v>
+        <v>20355</v>
       </c>
       <c r="C36" s="2">
-        <v>176983</v>
+        <v>176120</v>
       </c>
     </row>
   </sheetData>
@@ -981,10 +985,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C7" s="2">
-        <v>2528</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1036,7 +1040,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C12" s="2">
         <v>1177</v>
@@ -1047,10 +1051,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C13" s="2">
-        <v>1310</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1058,10 +1062,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C14" s="2">
-        <v>1191</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1113,10 +1117,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="C19" s="2">
-        <v>1501</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1124,10 +1128,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C20" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1135,10 +1139,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="C21" s="2">
-        <v>4547</v>
+        <v>4556</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1146,10 +1150,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>534</v>
+        <v>550</v>
       </c>
       <c r="C22" s="2">
-        <v>3355</v>
+        <v>3361</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1157,10 +1161,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="C23" s="2">
-        <v>14626</v>
+        <v>14638</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1168,10 +1172,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2356</v>
+        <v>2420</v>
       </c>
       <c r="C24" s="2">
-        <v>24446</v>
+        <v>24535</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1179,10 +1183,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C25" s="2">
-        <v>1448</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1190,10 +1194,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C26" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -1201,10 +1205,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C27" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -1212,10 +1216,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>957</v>
+        <v>972</v>
       </c>
       <c r="C28" s="2">
-        <v>8128</v>
+        <v>8538</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1223,10 +1227,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>689</v>
+        <v>672</v>
       </c>
       <c r="C29" s="2">
-        <v>8824</v>
+        <v>8719</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1245,10 +1249,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C31" s="2">
-        <v>1426</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1256,10 +1260,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C32" s="2">
-        <v>1326</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1267,10 +1271,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="C33" s="2">
-        <v>7347</v>
+        <v>7027</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1278,10 +1282,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="C34" s="2">
-        <v>2125</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1300,10 +1304,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>8251</v>
+        <v>8403</v>
       </c>
       <c r="C36" s="2">
-        <v>89581</v>
+        <v>89955</v>
       </c>
     </row>
   </sheetData>
@@ -1382,10 +1386,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C7" s="2">
-        <v>3521</v>
+        <v>3676</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1393,10 +1397,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C8" s="2">
-        <v>1741</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1404,7 +1408,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C9" s="2">
         <v>893</v>
@@ -1437,10 +1441,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C12" s="2">
-        <v>1016</v>
+        <v>995</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1448,10 +1452,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C13" s="2">
-        <v>907</v>
+        <v>968</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1459,10 +1463,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C14" s="2">
-        <v>1605</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1481,10 +1485,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C16" s="2">
-        <v>1497</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1514,10 +1518,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>479</v>
+        <v>498</v>
       </c>
       <c r="C19" s="2">
-        <v>2076</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1525,10 +1529,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="C20" s="2">
-        <v>1253</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1536,10 +1540,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>875</v>
+        <v>895</v>
       </c>
       <c r="C21" s="2">
-        <v>7222</v>
+        <v>7580</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1547,10 +1551,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1286</v>
+        <v>1333</v>
       </c>
       <c r="C22" s="2">
-        <v>8559</v>
+        <v>8906</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1558,10 +1562,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="C23" s="2">
-        <v>14170</v>
+        <v>14176</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1569,10 +1573,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2616</v>
+        <v>2692</v>
       </c>
       <c r="C24" s="2">
-        <v>22516</v>
+        <v>22635</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1580,10 +1584,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2">
-        <v>1526</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1591,10 +1595,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C26" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -1602,10 +1606,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C27" s="2">
-        <v>524</v>
+        <v>612</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -1613,10 +1617,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1414</v>
+        <v>1463</v>
       </c>
       <c r="C28" s="2">
-        <v>15850</v>
+        <v>15892</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -1624,10 +1628,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>788</v>
+        <v>779</v>
       </c>
       <c r="C29" s="2">
-        <v>10563</v>
+        <v>10497</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1646,10 +1650,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C31" s="2">
-        <v>1814</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1657,10 +1661,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="C32" s="2">
-        <v>1758</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1668,10 +1672,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>634</v>
+        <v>651</v>
       </c>
       <c r="C33" s="2">
-        <v>9059</v>
+        <v>8805</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1679,10 +1683,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>512</v>
+        <v>534</v>
       </c>
       <c r="C34" s="2">
-        <v>2577</v>
+        <v>2653</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1701,10 +1705,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>11135</v>
+        <v>11470</v>
       </c>
       <c r="C36" s="2">
-        <v>111672</v>
+        <v>112912</v>
       </c>
     </row>
   </sheetData>
@@ -1761,10 +1765,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5" s="2">
-        <v>171</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1783,10 +1787,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C7" s="2">
-        <v>3470</v>
+        <v>3719</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1794,10 +1798,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>60</v>
+        <v>205</v>
       </c>
       <c r="C8" s="2">
-        <v>366</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1805,21 +1809,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2">
-        <v>1019</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>37</v>
+      <c r="B10" s="2">
+        <v>23</v>
+      </c>
+      <c r="C10" s="2">
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1838,10 +1842,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C12" s="2">
-        <v>868</v>
+        <v>899</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -1849,10 +1853,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="C13" s="2">
-        <v>727</v>
+        <v>906</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -1860,10 +1864,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14" s="2">
-        <v>1023</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1882,10 +1886,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C16" s="2">
-        <v>1452</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -1915,10 +1919,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>515</v>
+        <v>552</v>
       </c>
       <c r="C19" s="2">
-        <v>2183</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1926,10 +1930,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>338</v>
+        <v>375</v>
       </c>
       <c r="C20" s="2">
-        <v>1558</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -1937,10 +1941,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>792</v>
+        <v>952</v>
       </c>
       <c r="C21" s="2">
-        <v>6565</v>
+        <v>7898</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1948,10 +1952,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1210</v>
+        <v>1402</v>
       </c>
       <c r="C22" s="2">
-        <v>7093</v>
+        <v>8287</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -1959,10 +1963,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="C23" s="2">
-        <v>14080</v>
+        <v>14518</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1970,10 +1974,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2473</v>
+        <v>2598</v>
       </c>
       <c r="C24" s="2">
-        <v>21351</v>
+        <v>25724</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -1981,10 +1985,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="C25" s="2">
-        <v>1357</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1992,10 +1996,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C26" s="2">
-        <v>485</v>
+        <v>518</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -2003,10 +2007,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C27" s="2">
-        <v>552</v>
+        <v>591</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -2014,10 +2018,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1307</v>
+        <v>1455</v>
       </c>
       <c r="C28" s="2">
-        <v>13232</v>
+        <v>16153</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2025,10 +2029,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>789</v>
+        <v>798</v>
       </c>
       <c r="C29" s="2">
-        <v>10621</v>
+        <v>11084</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2047,10 +2051,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="C31" s="2">
-        <v>2048</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -2058,10 +2062,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="C32" s="2">
-        <v>1552</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -2069,10 +2073,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>598</v>
+        <v>639</v>
       </c>
       <c r="C33" s="2">
-        <v>8602</v>
+        <v>8360</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2080,10 +2084,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>515</v>
+        <v>556</v>
       </c>
       <c r="C34" s="2">
-        <v>2611</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2102,10 +2106,411 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>10607</v>
+        <v>11705</v>
       </c>
       <c r="C36" s="2">
-        <v>103379</v>
+        <v>117319</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="58.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>218</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2917</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>44</v>
+      </c>
+      <c r="C8" s="2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>130</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>88</v>
+      </c>
+      <c r="C12" s="2">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>67</v>
+      </c>
+      <c r="C13" s="2">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>63</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>73</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2">
+        <v>480</v>
+      </c>
+      <c r="C19" s="2">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2">
+        <v>241</v>
+      </c>
+      <c r="C20" s="2">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2">
+        <v>626</v>
+      </c>
+      <c r="C21" s="2">
+        <v>5856</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2">
+        <v>582</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2">
+        <v>328</v>
+      </c>
+      <c r="C23" s="2">
+        <v>15068</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2">
+        <v>2348</v>
+      </c>
+      <c r="C24" s="2">
+        <v>21274</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2">
+        <v>159</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2">
+        <v>110</v>
+      </c>
+      <c r="C26" s="2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2">
+        <v>84</v>
+      </c>
+      <c r="C27" s="2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2">
+        <v>986</v>
+      </c>
+      <c r="C28" s="2">
+        <v>9570</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2">
+        <v>733</v>
+      </c>
+      <c r="C29" s="2">
+        <v>9231</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2">
+        <v>227</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="2">
+        <v>280</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2">
+        <v>572</v>
+      </c>
+      <c r="C33" s="2">
+        <v>6510</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="2">
+        <v>502</v>
+      </c>
+      <c r="C34" s="2">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="2">
+        <v>9018</v>
+      </c>
+      <c r="C36" s="2">
+        <v>90439</v>
       </c>
     </row>
   </sheetData>
@@ -2182,7 +2587,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C7" s="2">
         <v>5761</v>
@@ -2204,10 +2609,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C9" s="2">
-        <v>1959</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2317,7 +2722,7 @@
         <v>1401</v>
       </c>
       <c r="C19" s="2">
-        <v>6999</v>
+        <v>6984</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2325,10 +2730,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="C20" s="2">
-        <v>5877</v>
+        <v>5876</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2336,10 +2741,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>2026</v>
+        <v>2032</v>
       </c>
       <c r="C21" s="2">
-        <v>19142</v>
+        <v>19322</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2347,10 +2752,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>2169</v>
+        <v>2190</v>
       </c>
       <c r="C22" s="2">
-        <v>14589</v>
+        <v>14182</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2358,7 +2763,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="C23" s="2">
         <v>20200</v>
@@ -2369,10 +2774,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3340</v>
+        <v>3359</v>
       </c>
       <c r="C24" s="2">
-        <v>36235</v>
+        <v>36229</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2380,10 +2785,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C25" s="2">
-        <v>5559</v>
+        <v>5564</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -2413,10 +2818,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>3758</v>
+        <v>3767</v>
       </c>
       <c r="C28" s="2">
-        <v>32958</v>
+        <v>32939</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2424,10 +2829,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1807</v>
+        <v>1801</v>
       </c>
       <c r="C29" s="2">
-        <v>31758</v>
+        <v>31646</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2446,7 +2851,7 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C31" s="2">
         <v>8118</v>
@@ -2457,7 +2862,7 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>2917</v>
+        <v>2945</v>
       </c>
       <c r="C32" s="2">
         <v>21942</v>
@@ -2471,7 +2876,7 @@
         <v>926</v>
       </c>
       <c r="C33" s="2">
-        <v>11939</v>
+        <v>11422</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2479,10 +2884,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>1724</v>
+        <v>1732</v>
       </c>
       <c r="C34" s="2">
-        <v>8397</v>
+        <v>8427</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2501,10 +2906,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>25954</v>
+        <v>26047</v>
       </c>
       <c r="C36" s="2">
-        <v>253579</v>
+        <v>252716</v>
       </c>
     </row>
   </sheetData>
@@ -2583,7 +2988,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C7" s="2">
         <v>5331</v>
@@ -2605,10 +3010,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C9" s="2">
-        <v>1964</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -2649,10 +3054,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="C13" s="2">
-        <v>6569</v>
+        <v>6568</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -2715,10 +3120,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="C19" s="2">
-        <v>5682</v>
+        <v>5681</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2726,10 +3131,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C20" s="2">
-        <v>4089</v>
+        <v>4088</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -2737,10 +3142,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1831</v>
+        <v>1836</v>
       </c>
       <c r="C21" s="2">
-        <v>17604</v>
+        <v>17785</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -2748,10 +3153,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>1808</v>
+        <v>1827</v>
       </c>
       <c r="C22" s="2">
-        <v>12080</v>
+        <v>11681</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -2759,7 +3164,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="C23" s="2">
         <v>19455</v>
@@ -2770,10 +3175,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>3087</v>
+        <v>3109</v>
       </c>
       <c r="C24" s="2">
-        <v>34500</v>
+        <v>34496</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -2781,10 +3186,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C25" s="2">
-        <v>5570</v>
+        <v>5569</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -2814,10 +3219,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>3622</v>
+        <v>3631</v>
       </c>
       <c r="C28" s="2">
-        <v>29512</v>
+        <v>29494</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -2825,10 +3230,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1650</v>
+        <v>1646</v>
       </c>
       <c r="C29" s="2">
-        <v>21215</v>
+        <v>21105</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -2847,7 +3252,7 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C31" s="2">
         <v>6882</v>
@@ -2858,7 +3263,7 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>1546</v>
+        <v>1550</v>
       </c>
       <c r="C32" s="2">
         <v>10093</v>
@@ -2872,7 +3277,7 @@
         <v>906</v>
       </c>
       <c r="C33" s="2">
-        <v>11441</v>
+        <v>10939</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2880,10 +3285,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="C34" s="2">
-        <v>5698</v>
+        <v>5691</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -2902,10 +3307,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>21983</v>
+        <v>22064</v>
       </c>
       <c r="C36" s="2">
-        <v>215096</v>
+        <v>214232</v>
       </c>
     </row>
   </sheetData>
@@ -2984,7 +3389,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C7" s="2">
         <v>3679</v>
@@ -3039,7 +3444,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C12" s="2">
         <v>2454</v>
@@ -3050,10 +3455,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="C13" s="2">
-        <v>5775</v>
+        <v>5582</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -3116,10 +3521,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C19" s="2">
-        <v>2713</v>
+        <v>2711</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -3127,10 +3532,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C20" s="2">
-        <v>1470</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -3138,10 +3543,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>1177</v>
+        <v>1186</v>
       </c>
       <c r="C21" s="2">
-        <v>10990</v>
+        <v>11191</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3149,10 +3554,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="C22" s="2">
-        <v>5672</v>
+        <v>5477</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3160,10 +3565,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="C23" s="2">
-        <v>29686</v>
+        <v>29682</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -3171,10 +3576,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>2270</v>
+        <v>2292</v>
       </c>
       <c r="C24" s="2">
-        <v>25287</v>
+        <v>25284</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -3182,10 +3587,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C25" s="2">
-        <v>3765</v>
+        <v>3757</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -3215,10 +3620,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>2124</v>
+        <v>2129</v>
       </c>
       <c r="C28" s="2">
-        <v>17723</v>
+        <v>17709</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -3226,10 +3631,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>1144</v>
+        <v>1137</v>
       </c>
       <c r="C29" s="2">
-        <v>15430</v>
+        <v>15315</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -3273,7 +3678,7 @@
         <v>528</v>
       </c>
       <c r="C33" s="2">
-        <v>6091</v>
+        <v>5627</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -3281,10 +3686,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="C34" s="2">
-        <v>3499</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -3303,10 +3708,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>13573</v>
+        <v>13644</v>
       </c>
       <c r="C36" s="2">
-        <v>152218</v>
+        <v>151411</v>
       </c>
     </row>
   </sheetData>
@@ -3385,7 +3790,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C7" s="2">
         <v>2658</v>
@@ -3440,7 +3845,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2">
         <v>1907</v>
@@ -3451,10 +3856,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="C13" s="2">
-        <v>3797</v>
+        <v>3988</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -3517,10 +3922,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C19" s="2">
-        <v>1810</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -3539,10 +3944,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="C21" s="2">
-        <v>7894</v>
+        <v>8057</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3550,10 +3955,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C22" s="2">
-        <v>3726</v>
+        <v>3537</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3561,10 +3966,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C23" s="2">
-        <v>16524</v>
+        <v>16522</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -3572,10 +3977,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1795</v>
+        <v>1812</v>
       </c>
       <c r="C24" s="2">
-        <v>20681</v>
+        <v>20678</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -3583,10 +3988,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C25" s="2">
-        <v>2699</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -3616,10 +4021,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1526</v>
+        <v>1530</v>
       </c>
       <c r="C28" s="2">
-        <v>12738</v>
+        <v>12724</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -3627,10 +4032,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="C29" s="2">
-        <v>10909</v>
+        <v>10869</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -3682,10 +4087,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C34" s="2">
-        <v>2527</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -3704,10 +4109,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>10227</v>
+        <v>10284</v>
       </c>
       <c r="C36" s="2">
-        <v>104353</v>
+        <v>104444</v>
       </c>
     </row>
   </sheetData>
@@ -3786,7 +4191,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C7" s="2">
         <v>1855</v>
@@ -3808,10 +4213,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C9" s="2">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -3841,7 +4246,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C12" s="2">
         <v>1702</v>
@@ -3852,7 +4257,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="C13" s="2">
         <v>2743</v>
@@ -3885,10 +4290,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C16" s="2">
-        <v>1806</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -3940,10 +4345,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="C21" s="2">
-        <v>6550</v>
+        <v>6704</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3951,10 +4356,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C22" s="2">
-        <v>3014</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3962,10 +4367,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="C23" s="2">
-        <v>16191</v>
+        <v>16189</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -3973,7 +4378,7 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1561</v>
+        <v>1576</v>
       </c>
       <c r="C24" s="2">
         <v>18605</v>
@@ -3984,10 +4389,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C25" s="2">
-        <v>2358</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -4017,10 +4422,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1279</v>
+        <v>1287</v>
       </c>
       <c r="C28" s="2">
-        <v>10270</v>
+        <v>10256</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -4028,10 +4433,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="C29" s="2">
-        <v>9732</v>
+        <v>9634</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -4083,10 +4488,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C34" s="2">
-        <v>2049</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -4105,10 +4510,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>8693</v>
+        <v>8749</v>
       </c>
       <c r="C36" s="2">
-        <v>90112</v>
+        <v>89968</v>
       </c>
     </row>
   </sheetData>
@@ -4187,10 +4592,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C7" s="2">
-        <v>1450</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -4209,10 +4614,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -4234,7 +4639,7 @@
         <v>17</v>
       </c>
       <c r="C11" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -4242,10 +4647,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C12" s="2">
-        <v>1169</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -4264,10 +4669,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C14" s="2">
-        <v>2403</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -4322,7 +4727,7 @@
         <v>278</v>
       </c>
       <c r="C19" s="2">
-        <v>906</v>
+        <v>939</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -4330,7 +4735,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C20" s="2">
         <v>384</v>
@@ -4341,10 +4746,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C21" s="2">
-        <v>3918</v>
+        <v>3954</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -4352,10 +4757,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C22" s="2">
-        <v>2072</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -4363,10 +4768,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="C23" s="2">
-        <v>15425</v>
+        <v>15438</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -4374,10 +4779,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1168</v>
+        <v>1182</v>
       </c>
       <c r="C24" s="2">
-        <v>14089</v>
+        <v>14796</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -4385,10 +4790,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C25" s="2">
-        <v>1897</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -4396,10 +4801,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C26" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -4410,7 +4815,7 @@
         <v>42</v>
       </c>
       <c r="C27" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -4418,10 +4823,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="C28" s="2">
-        <v>7064</v>
+        <v>7192</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -4429,10 +4834,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>668</v>
+        <v>615</v>
       </c>
       <c r="C29" s="2">
-        <v>7729</v>
+        <v>7593</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -4462,10 +4867,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C32" s="2">
-        <v>762</v>
+        <v>788</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -4476,7 +4881,7 @@
         <v>144</v>
       </c>
       <c r="C33" s="2">
-        <v>1366</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -4484,7 +4889,7 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C34" s="2">
         <v>1314</v>
@@ -4506,10 +4911,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>6027</v>
+        <v>6021</v>
       </c>
       <c r="C36" s="2">
-        <v>67960</v>
+        <v>69226</v>
       </c>
     </row>
   </sheetData>
@@ -4588,10 +4993,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C7" s="2">
-        <v>1428</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -4610,10 +5015,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -4643,7 +5048,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C12" s="2">
         <v>1355</v>
@@ -4665,10 +5070,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C14" s="2">
-        <v>1791</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -4720,10 +5125,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C19" s="2">
-        <v>1112</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -4731,7 +5136,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C20" s="2">
         <v>354</v>
@@ -4742,10 +5147,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C21" s="2">
-        <v>5397.8</v>
+        <v>3918</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -4753,10 +5158,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C22" s="2">
-        <v>1847</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -4764,10 +5169,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C23" s="2">
-        <v>14584</v>
+        <v>14581</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -4775,10 +5180,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1327</v>
+        <v>1344</v>
       </c>
       <c r="C24" s="2">
-        <v>17931.8</v>
+        <v>16047</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -4786,10 +5191,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C25" s="2">
-        <v>1818</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -4797,10 +5202,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C26" s="2">
-        <v>3306.8</v>
+        <v>437</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -4819,10 +5224,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="C28" s="2">
-        <v>6573</v>
+        <v>6571</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -4830,10 +5235,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>652</v>
+        <v>601</v>
       </c>
       <c r="C29" s="2">
-        <v>7799</v>
+        <v>7652</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -4852,10 +5257,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C31" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -4863,7 +5268,7 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C32" s="2">
         <v>778</v>
@@ -4874,10 +5279,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C33" s="2">
-        <v>1562</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -4885,10 +5290,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C34" s="2">
-        <v>1436</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -4907,10 +5312,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>6270</v>
+        <v>6279</v>
       </c>
       <c r="C36" s="2">
-        <v>74692.399999999994</v>
+        <v>68324</v>
       </c>
     </row>
   </sheetData>
@@ -4989,7 +5394,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C7" s="2">
         <v>1845</v>
@@ -5011,10 +5416,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -5044,10 +5449,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2">
-        <v>1246</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -5066,10 +5471,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C14" s="2">
-        <v>2110</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -5121,10 +5526,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C19" s="2">
-        <v>1414</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -5132,10 +5537,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C20" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -5143,10 +5548,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="C21" s="6">
-        <v>4234.7</v>
+        <v>4452</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -5154,10 +5559,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C22" s="2">
-        <v>2952</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -5165,10 +5570,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C23" s="2">
-        <v>14481</v>
+        <v>14473</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -5176,10 +5581,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2">
-        <v>1966</v>
+        <v>1997</v>
       </c>
       <c r="C24" s="6">
-        <v>21646</v>
+        <v>21130</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -5187,10 +5592,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C25" s="2">
-        <v>1918</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -5198,10 +5603,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C26" s="6">
-        <v>1350</v>
+        <v>427</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -5220,10 +5625,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="C28" s="2">
-        <v>9142</v>
+        <v>9103</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -5231,10 +5636,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>713</v>
+        <v>662</v>
       </c>
       <c r="C29" s="2">
-        <v>8324.5499999999993</v>
+        <v>8374</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -5253,10 +5658,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C31" s="2">
-        <v>1184</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -5264,10 +5669,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C32" s="2">
-        <v>1158</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -5275,10 +5680,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C33" s="2">
-        <v>4568</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -5286,10 +5691,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="C34" s="2">
-        <v>2031</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -5308,10 +5713,10 @@
         <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>7981</v>
+        <v>8003</v>
       </c>
       <c r="C36" s="6">
-        <v>84857.25</v>
+        <v>83094</v>
       </c>
     </row>
   </sheetData>
